--- a/research/traditional_assets/database/data/australia/australia_utility_water.xlsx
+++ b/research/traditional_assets/database/data/australia/australia_utility_water.xlsx
@@ -1404,7 +1404,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1541,22 +1541,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.06417717306941925</v>
+        <v>0.06401614155021099</v>
       </c>
       <c r="C2">
-        <v>184.6041442913227</v>
+        <v>183.0402040814586</v>
       </c>
       <c r="D2">
-        <v>182.0641442913227</v>
+        <v>182.5022040814586</v>
       </c>
       <c r="E2">
-        <v>-70.40000000000001</v>
+        <v>-68.39800000000001</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>2.002</v>
       </c>
       <c r="G2">
         <v>2.54</v>
@@ -1577,28 +1577,28 @@
         <v>17.5</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.1007006</v>
       </c>
       <c r="N2">
-        <v>17.5</v>
+        <v>17.3992994</v>
       </c>
       <c r="O2">
-        <v>5.25</v>
+        <v>5.21978982</v>
       </c>
       <c r="P2">
-        <v>12.25</v>
+        <v>12.17950958</v>
       </c>
       <c r="Q2">
-        <v>-5.25</v>
+        <v>-5.320490419999999</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.06417717306941925</v>
+        <v>0.0643071126769808</v>
       </c>
       <c r="T2">
-        <v>0.4244150824346247</v>
+        <v>0.4274159971589099</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1615,7 +1615,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>173.7824799455018</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1623,22 +1623,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.06401614155021099</v>
+        <v>0.06385511003100275</v>
       </c>
       <c r="C3">
-        <v>183.0402040814586</v>
+        <v>181.4783769643285</v>
       </c>
       <c r="D3">
-        <v>182.5022040814586</v>
+        <v>182.9423769643285</v>
       </c>
       <c r="E3">
-        <v>-68.39800000000001</v>
+        <v>-66.396</v>
       </c>
       <c r="F3">
-        <v>2.002</v>
+        <v>4.004</v>
       </c>
       <c r="G3">
         <v>2.54</v>
@@ -1659,28 +1659,28 @@
         <v>17.5</v>
       </c>
       <c r="M3">
-        <v>0.1007006</v>
+        <v>0.2014012</v>
       </c>
       <c r="N3">
-        <v>17.3992994</v>
+        <v>17.2985988</v>
       </c>
       <c r="O3">
-        <v>5.21978982</v>
+        <v>5.18957964</v>
       </c>
       <c r="P3">
-        <v>12.17950958</v>
+        <v>12.10901916</v>
       </c>
       <c r="Q3">
-        <v>-5.320490419999999</v>
+        <v>-5.390980839999999</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.0643071126769808</v>
+        <v>0.0644397041132681</v>
       </c>
       <c r="T3">
-        <v>0.4274159971589099</v>
+        <v>0.4304781550408336</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1697,7 +1697,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>173.7824799455018</v>
+        <v>86.89123997275091</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1705,22 +1705,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.06385511003100275</v>
+        <v>0.06369407851179448</v>
       </c>
       <c r="C4">
-        <v>181.4783769643285</v>
+        <v>179.9186782664579</v>
       </c>
       <c r="D4">
-        <v>182.9423769643285</v>
+        <v>183.3846782664579</v>
       </c>
       <c r="E4">
-        <v>-66.396</v>
+        <v>-64.39400000000001</v>
       </c>
       <c r="F4">
-        <v>4.004</v>
+        <v>6.006</v>
       </c>
       <c r="G4">
         <v>2.54</v>
@@ -1741,28 +1741,28 @@
         <v>17.5</v>
       </c>
       <c r="M4">
-        <v>0.2014012</v>
+        <v>0.3021018</v>
       </c>
       <c r="N4">
-        <v>17.2985988</v>
+        <v>17.1978982</v>
       </c>
       <c r="O4">
-        <v>5.18957964</v>
+        <v>5.15936946</v>
       </c>
       <c r="P4">
-        <v>12.10901916</v>
+        <v>12.03852874</v>
       </c>
       <c r="Q4">
-        <v>-5.390980839999999</v>
+        <v>-5.46147126</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.0644397041132681</v>
+        <v>0.06457502939360256</v>
       </c>
       <c r="T4">
-        <v>0.4304781550408336</v>
+        <v>0.4336034501986732</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1779,7 +1779,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>86.89123997275091</v>
+        <v>57.92749331516728</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1787,22 +1787,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.06369407851179448</v>
+        <v>0.06353304699258622</v>
       </c>
       <c r="C5">
-        <v>179.9186782664579</v>
+        <v>178.3611234629519</v>
       </c>
       <c r="D5">
-        <v>183.3846782664579</v>
+        <v>183.8291234629519</v>
       </c>
       <c r="E5">
-        <v>-64.39400000000001</v>
+        <v>-62.392</v>
       </c>
       <c r="F5">
-        <v>6.006</v>
+        <v>8.008000000000001</v>
       </c>
       <c r="G5">
         <v>2.54</v>
@@ -1823,28 +1823,28 @@
         <v>17.5</v>
       </c>
       <c r="M5">
-        <v>0.3021018</v>
+        <v>0.4028024</v>
       </c>
       <c r="N5">
-        <v>17.1978982</v>
+        <v>17.0971976</v>
       </c>
       <c r="O5">
-        <v>5.15936946</v>
+        <v>5.129159280000001</v>
       </c>
       <c r="P5">
-        <v>12.03852874</v>
+        <v>11.96803832</v>
       </c>
       <c r="Q5">
-        <v>-5.46147126</v>
+        <v>-5.531961679999998</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.06457502939360256</v>
+        <v>0.06471317395061064</v>
       </c>
       <c r="T5">
-        <v>0.4336034501986732</v>
+        <v>0.4367938556723012</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1861,7 +1861,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>57.92749331516728</v>
+        <v>43.44561998637545</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1869,22 +1869,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.06353304699258622</v>
+        <v>0.06337201547337797</v>
       </c>
       <c r="C6">
-        <v>178.3611234629519</v>
+        <v>176.8057281792996</v>
       </c>
       <c r="D6">
-        <v>183.8291234629519</v>
+        <v>184.2757281792996</v>
       </c>
       <c r="E6">
-        <v>-62.392</v>
+        <v>-60.39</v>
       </c>
       <c r="F6">
-        <v>8.008000000000001</v>
+        <v>10.01</v>
       </c>
       <c r="G6">
         <v>2.54</v>
@@ -1905,28 +1905,28 @@
         <v>17.5</v>
       </c>
       <c r="M6">
-        <v>0.4028024</v>
+        <v>0.503503</v>
       </c>
       <c r="N6">
-        <v>17.0971976</v>
+        <v>16.996497</v>
       </c>
       <c r="O6">
-        <v>5.129159280000001</v>
+        <v>5.0989491</v>
       </c>
       <c r="P6">
-        <v>11.96803832</v>
+        <v>11.8975479</v>
       </c>
       <c r="Q6">
-        <v>-5.531961679999998</v>
+        <v>-5.602452099999999</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.06471317395061064</v>
+        <v>0.06485422681408207</v>
       </c>
       <c r="T6">
-        <v>0.4367938556723012</v>
+        <v>0.440051427576953</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1943,7 +1943,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>43.44561998637545</v>
+        <v>34.75649598910037</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1951,22 +1951,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.06337201547337797</v>
+        <v>0.0632109839541697</v>
       </c>
       <c r="C7">
-        <v>176.8057281792996</v>
+        <v>175.252508193206</v>
       </c>
       <c r="D7">
-        <v>184.2757281792996</v>
+        <v>184.724508193206</v>
       </c>
       <c r="E7">
-        <v>-60.39</v>
+        <v>-58.38800000000001</v>
       </c>
       <c r="F7">
-        <v>10.01</v>
+        <v>12.012</v>
       </c>
       <c r="G7">
         <v>2.54</v>
@@ -1987,28 +1987,28 @@
         <v>17.5</v>
       </c>
       <c r="M7">
-        <v>0.503503</v>
+        <v>0.6042036000000001</v>
       </c>
       <c r="N7">
-        <v>16.996497</v>
+        <v>16.8957964</v>
       </c>
       <c r="O7">
-        <v>5.0989491</v>
+        <v>5.068738919999999</v>
       </c>
       <c r="P7">
-        <v>11.8975479</v>
+        <v>11.82705748</v>
       </c>
       <c r="Q7">
-        <v>-5.602452099999999</v>
+        <v>-5.672942520000001</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.06485422681408207</v>
+        <v>0.0649982808023082</v>
       </c>
       <c r="T7">
-        <v>0.440051427576953</v>
+        <v>0.4433783095221292</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -2025,7 +2025,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>34.75649598910037</v>
+        <v>28.96374665758363</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -2033,22 +2033,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.0632109839541697</v>
+        <v>0.06304995243496146</v>
       </c>
       <c r="C8">
-        <v>175.252508193206</v>
+        <v>173.7014794364493</v>
       </c>
       <c r="D8">
-        <v>184.724508193206</v>
+        <v>185.1754794364494</v>
       </c>
       <c r="E8">
-        <v>-58.38800000000001</v>
+        <v>-56.38600000000001</v>
       </c>
       <c r="F8">
-        <v>12.012</v>
+        <v>14.014</v>
       </c>
       <c r="G8">
         <v>2.54</v>
@@ -2069,28 +2069,28 @@
         <v>17.5</v>
       </c>
       <c r="M8">
-        <v>0.6042036</v>
+        <v>0.7049042</v>
       </c>
       <c r="N8">
-        <v>16.8957964</v>
+        <v>16.7950958</v>
       </c>
       <c r="O8">
-        <v>5.06873892</v>
+        <v>5.038528739999999</v>
       </c>
       <c r="P8">
-        <v>11.82705748</v>
+        <v>11.75656706</v>
       </c>
       <c r="Q8">
-        <v>-5.672942519999999</v>
+        <v>-5.743432940000002</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.0649982808023082</v>
+        <v>0.06514543272576501</v>
       </c>
       <c r="T8">
-        <v>0.4433783095221292</v>
+        <v>0.4467767373155889</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -2107,7 +2107,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>28.96374665758364</v>
+        <v>24.82606856364312</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -2115,22 +2115,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.06304995243496145</v>
+        <v>0.0628889209157532</v>
       </c>
       <c r="C9">
-        <v>173.7014794364494</v>
+        <v>172.1526579967672</v>
       </c>
       <c r="D9">
-        <v>185.1754794364494</v>
+        <v>185.6286579967672</v>
       </c>
       <c r="E9">
-        <v>-56.386</v>
+        <v>-54.384</v>
       </c>
       <c r="F9">
-        <v>14.014</v>
+        <v>16.016</v>
       </c>
       <c r="G9">
         <v>2.54</v>
@@ -2151,28 +2151,28 @@
         <v>17.5</v>
       </c>
       <c r="M9">
-        <v>0.7049042000000001</v>
+        <v>0.8056048</v>
       </c>
       <c r="N9">
-        <v>16.7950958</v>
+        <v>16.6943952</v>
       </c>
       <c r="O9">
-        <v>5.038528739999999</v>
+        <v>5.008318559999999</v>
       </c>
       <c r="P9">
-        <v>11.75656706</v>
+        <v>11.68607664</v>
       </c>
       <c r="Q9">
-        <v>-5.743432940000002</v>
+        <v>-5.81392336</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.06514543272576501</v>
+        <v>0.06529578360407956</v>
       </c>
       <c r="T9">
-        <v>0.4467767373155889</v>
+        <v>0.4502490439741237</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2189,7 +2189,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>24.82606856364311</v>
+        <v>21.72280999318772</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2197,22 +2197,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.0628889209157532</v>
+        <v>0.06272788939654493</v>
       </c>
       <c r="C10">
-        <v>172.1526579967672</v>
+        <v>170.6060601197686</v>
       </c>
       <c r="D10">
-        <v>185.6286579967672</v>
+        <v>186.0840601197687</v>
       </c>
       <c r="E10">
-        <v>-54.384</v>
+        <v>-52.38200000000001</v>
       </c>
       <c r="F10">
-        <v>16.016</v>
+        <v>18.018</v>
       </c>
       <c r="G10">
         <v>2.54</v>
@@ -2233,28 +2233,28 @@
         <v>17.5</v>
       </c>
       <c r="M10">
-        <v>0.8056048</v>
+        <v>0.9063054</v>
       </c>
       <c r="N10">
-        <v>16.6943952</v>
+        <v>16.5936946</v>
       </c>
       <c r="O10">
-        <v>5.008318559999999</v>
+        <v>4.978108379999999</v>
       </c>
       <c r="P10">
-        <v>11.68607664</v>
+        <v>11.61558622</v>
       </c>
       <c r="Q10">
-        <v>-5.81392336</v>
+        <v>-5.884413779999999</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.06529578360407956</v>
+        <v>0.06544943889730212</v>
       </c>
       <c r="T10">
-        <v>0.4502490439741237</v>
+        <v>0.4537976650647141</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2271,7 +2271,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>21.72280999318772</v>
+        <v>19.30916443838909</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2279,22 +2279,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.06272788939654493</v>
+        <v>0.06256685787733667</v>
       </c>
       <c r="C11">
-        <v>170.6060601197686</v>
+        <v>169.0617022108763</v>
       </c>
       <c r="D11">
-        <v>186.0840601197687</v>
+        <v>186.5417022108763</v>
       </c>
       <c r="E11">
-        <v>-52.38200000000001</v>
+        <v>-50.38000000000001</v>
       </c>
       <c r="F11">
-        <v>18.018</v>
+        <v>20.02</v>
       </c>
       <c r="G11">
         <v>2.54</v>
@@ -2315,28 +2315,28 @@
         <v>17.5</v>
       </c>
       <c r="M11">
-        <v>0.9063054</v>
+        <v>1.007006</v>
       </c>
       <c r="N11">
-        <v>16.5936946</v>
+        <v>16.492994</v>
       </c>
       <c r="O11">
-        <v>4.978108379999999</v>
+        <v>4.9478982</v>
       </c>
       <c r="P11">
-        <v>11.61558622</v>
+        <v>11.5450958</v>
       </c>
       <c r="Q11">
-        <v>-5.884413779999999</v>
+        <v>-5.954904200000001</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.06544943889730212</v>
+        <v>0.0656065087525963</v>
       </c>
       <c r="T11">
-        <v>0.4537976650647141</v>
+        <v>0.4574251444017622</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2353,7 +2353,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>19.30916443838909</v>
+        <v>17.37824799455018</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2361,22 +2361,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.06256685787733667</v>
+        <v>0.06240582635812841</v>
       </c>
       <c r="C12">
-        <v>169.0617022108763</v>
+        <v>167.5196008372958</v>
       </c>
       <c r="D12">
-        <v>186.5417022108763</v>
+        <v>187.0016008372958</v>
       </c>
       <c r="E12">
-        <v>-50.38</v>
+        <v>-48.378</v>
       </c>
       <c r="F12">
-        <v>20.02</v>
+        <v>22.022</v>
       </c>
       <c r="G12">
         <v>2.54</v>
@@ -2397,28 +2397,28 @@
         <v>17.5</v>
       </c>
       <c r="M12">
-        <v>1.007006</v>
+        <v>1.1077066</v>
       </c>
       <c r="N12">
-        <v>16.492994</v>
+        <v>16.3922934</v>
       </c>
       <c r="O12">
-        <v>4.9478982</v>
+        <v>4.91768802</v>
       </c>
       <c r="P12">
-        <v>11.5450958</v>
+        <v>11.47460538</v>
       </c>
       <c r="Q12">
-        <v>-5.954904200000001</v>
+        <v>-6.02539462</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.0656065087525963</v>
+        <v>0.06576710826756002</v>
       </c>
       <c r="T12">
-        <v>0.4574251444017622</v>
+        <v>0.4611341401284069</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2435,7 +2435,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>17.37824799455018</v>
+        <v>15.79840726777289</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2443,22 +2443,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.06240582635812841</v>
+        <v>0.06224479483892015</v>
       </c>
       <c r="C13">
-        <v>167.5196008372958</v>
+        <v>165.9797727300155</v>
       </c>
       <c r="D13">
-        <v>187.0016008372958</v>
+        <v>187.4637727300155</v>
       </c>
       <c r="E13">
-        <v>-48.378</v>
+        <v>-46.376</v>
       </c>
       <c r="F13">
-        <v>22.022</v>
+        <v>24.024</v>
       </c>
       <c r="G13">
         <v>2.54</v>
@@ -2479,28 +2479,28 @@
         <v>17.5</v>
       </c>
       <c r="M13">
-        <v>1.1077066</v>
+        <v>1.2084072</v>
       </c>
       <c r="N13">
-        <v>16.3922934</v>
+        <v>16.2915928</v>
       </c>
       <c r="O13">
-        <v>4.91768802</v>
+        <v>4.88747784</v>
       </c>
       <c r="P13">
-        <v>11.47460538</v>
+        <v>11.40411496</v>
       </c>
       <c r="Q13">
-        <v>-6.02539462</v>
+        <v>-6.095885039999999</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.06576710826756002</v>
+        <v>0.06593135777150018</v>
       </c>
       <c r="T13">
-        <v>0.4611341401284069</v>
+        <v>0.4649274312124753</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2517,7 +2517,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>15.79840726777289</v>
+        <v>14.48187332879182</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2525,22 +2525,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.06224479483892015</v>
+        <v>0.0620837633197119</v>
       </c>
       <c r="C14">
-        <v>165.9797727300155</v>
+        <v>164.442234785835</v>
       </c>
       <c r="D14">
-        <v>187.4637727300155</v>
+        <v>187.928234785835</v>
       </c>
       <c r="E14">
-        <v>-46.376</v>
+        <v>-44.374</v>
       </c>
       <c r="F14">
-        <v>24.024</v>
+        <v>26.026</v>
       </c>
       <c r="G14">
         <v>2.54</v>
@@ -2561,28 +2561,28 @@
         <v>17.5</v>
       </c>
       <c r="M14">
-        <v>1.2084072</v>
+        <v>1.3091078</v>
       </c>
       <c r="N14">
-        <v>16.2915928</v>
+        <v>16.1908922</v>
       </c>
       <c r="O14">
-        <v>4.88747784</v>
+        <v>4.85726766</v>
       </c>
       <c r="P14">
-        <v>11.40411496</v>
+        <v>11.33362454</v>
       </c>
       <c r="Q14">
-        <v>-6.095885039999999</v>
+        <v>-6.166375459999999</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.06593135777150018</v>
+        <v>0.06609938312610564</v>
       </c>
       <c r="T14">
-        <v>0.4649274312124753</v>
+        <v>0.4688079243904303</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2599,7 +2599,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>14.48187332879182</v>
+        <v>13.36788307273091</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2607,22 +2607,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.0620837633197119</v>
+        <v>0.06206973180050365</v>
       </c>
       <c r="C15">
-        <v>164.442234785835</v>
+        <v>162.4808148281172</v>
       </c>
       <c r="D15">
-        <v>187.928234785835</v>
+        <v>187.9688148281172</v>
       </c>
       <c r="E15">
-        <v>-44.374</v>
+        <v>-42.372</v>
       </c>
       <c r="F15">
-        <v>26.026</v>
+        <v>28.02800000000001</v>
       </c>
       <c r="G15">
         <v>2.54</v>
@@ -2643,45 +2643,45 @@
         <v>17.5</v>
       </c>
       <c r="M15">
-        <v>1.3091078</v>
+        <v>1.4518504</v>
       </c>
       <c r="N15">
-        <v>16.1908922</v>
+        <v>16.0481496</v>
       </c>
       <c r="O15">
-        <v>4.85726766</v>
+        <v>4.814444879999999</v>
       </c>
       <c r="P15">
-        <v>11.33362454</v>
+        <v>11.23370472</v>
       </c>
       <c r="Q15">
-        <v>-6.166375459999999</v>
+        <v>-6.266295280000001</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.06609938312610564</v>
+        <v>0.06627131604709727</v>
       </c>
       <c r="T15">
-        <v>0.4688079243904303</v>
+        <v>0.4727786615957796</v>
       </c>
       <c r="U15">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V15">
         <v>0.3</v>
       </c>
       <c r="W15">
-        <v>0.03521</v>
+        <v>0.03625999999999999</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y15">
-        <v>13.36788307273091</v>
+        <v>12.05358348215491</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2689,22 +2689,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.06206973180050365</v>
+        <v>0.06191920028129538</v>
       </c>
       <c r="C16">
-        <v>162.4808148281172</v>
+        <v>160.9152665879898</v>
       </c>
       <c r="D16">
-        <v>187.9688148281172</v>
+        <v>188.4052665879898</v>
       </c>
       <c r="E16">
-        <v>-42.372</v>
+        <v>-40.37</v>
       </c>
       <c r="F16">
-        <v>28.02800000000001</v>
+        <v>30.03000000000001</v>
       </c>
       <c r="G16">
         <v>2.54</v>
@@ -2725,28 +2725,28 @@
         <v>17.5</v>
       </c>
       <c r="M16">
-        <v>1.4518504</v>
+        <v>1.555554</v>
       </c>
       <c r="N16">
-        <v>16.0481496</v>
+        <v>15.944446</v>
       </c>
       <c r="O16">
-        <v>4.814444879999999</v>
+        <v>4.783333799999999</v>
       </c>
       <c r="P16">
-        <v>11.23370472</v>
+        <v>11.1611122</v>
       </c>
       <c r="Q16">
-        <v>-6.266295280000001</v>
+        <v>-6.3388878</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.06627131604709727</v>
+        <v>0.0664472944485828</v>
       </c>
       <c r="T16">
-        <v>0.4727786615957796</v>
+        <v>0.4768428279118431</v>
       </c>
       <c r="U16">
         <v>0.0518</v>
@@ -2763,7 +2763,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>12.05358348215491</v>
+        <v>11.25001125001125</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2771,22 +2771,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.06191920028129538</v>
+        <v>0.06176866876208712</v>
       </c>
       <c r="C17">
-        <v>160.9152665879898</v>
+        <v>159.3517498920244</v>
       </c>
       <c r="D17">
-        <v>188.4052665879898</v>
+        <v>188.8437498920244</v>
       </c>
       <c r="E17">
-        <v>-40.37</v>
+        <v>-38.368</v>
       </c>
       <c r="F17">
-        <v>30.03</v>
+        <v>32.032</v>
       </c>
       <c r="G17">
         <v>2.54</v>
@@ -2807,28 +2807,28 @@
         <v>17.5</v>
       </c>
       <c r="M17">
-        <v>1.555554</v>
+        <v>1.6592576</v>
       </c>
       <c r="N17">
-        <v>15.944446</v>
+        <v>15.8407424</v>
       </c>
       <c r="O17">
-        <v>4.783333799999999</v>
+        <v>4.75222272</v>
       </c>
       <c r="P17">
-        <v>11.1611122</v>
+        <v>11.08851968</v>
       </c>
       <c r="Q17">
-        <v>-6.3388878</v>
+        <v>-6.411480319999999</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.0664472944485828</v>
+        <v>0.06662746281200849</v>
       </c>
       <c r="T17">
-        <v>0.4768428279118431</v>
+        <v>0.4810037600925747</v>
       </c>
       <c r="U17">
         <v>0.0518</v>
@@ -2845,7 +2845,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>11.25001125001125</v>
+        <v>10.54688554688555</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2853,22 +2853,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.06176866876208712</v>
+        <v>0.06161813724287887</v>
       </c>
       <c r="C18">
-        <v>159.3517498920244</v>
+        <v>157.790278957598</v>
       </c>
       <c r="D18">
-        <v>188.8437498920244</v>
+        <v>189.284278957598</v>
       </c>
       <c r="E18">
-        <v>-38.368</v>
+        <v>-36.366</v>
       </c>
       <c r="F18">
-        <v>32.032</v>
+        <v>34.03400000000001</v>
       </c>
       <c r="G18">
         <v>2.54</v>
@@ -2889,28 +2889,28 @@
         <v>17.5</v>
       </c>
       <c r="M18">
-        <v>1.6592576</v>
+        <v>1.7629612</v>
       </c>
       <c r="N18">
-        <v>15.8407424</v>
+        <v>15.7370388</v>
       </c>
       <c r="O18">
-        <v>4.75222272</v>
+        <v>4.72111164</v>
       </c>
       <c r="P18">
-        <v>11.08851968</v>
+        <v>11.01592716</v>
       </c>
       <c r="Q18">
-        <v>-6.411480319999999</v>
+        <v>-6.48407284</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.06662746281200849</v>
+        <v>0.06681197258178177</v>
       </c>
       <c r="T18">
-        <v>0.4810037600925747</v>
+        <v>0.4852649556993481</v>
       </c>
       <c r="U18">
         <v>0.0518</v>
@@ -2927,7 +2927,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>10.54688554688555</v>
+        <v>9.926480514715808</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2935,22 +2935,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.06161813724287887</v>
+        <v>0.06168180572367062</v>
       </c>
       <c r="C19">
-        <v>157.790278957598</v>
+        <v>155.6017031850347</v>
       </c>
       <c r="D19">
-        <v>189.284278957598</v>
+        <v>189.0977031850347</v>
       </c>
       <c r="E19">
-        <v>-36.366</v>
+        <v>-34.364</v>
       </c>
       <c r="F19">
-        <v>34.03400000000001</v>
+        <v>36.03600000000001</v>
       </c>
       <c r="G19">
         <v>2.54</v>
@@ -2971,45 +2971,45 @@
         <v>17.5</v>
       </c>
       <c r="M19">
-        <v>1.7629612</v>
+        <v>1.927926</v>
       </c>
       <c r="N19">
-        <v>15.7370388</v>
+        <v>15.572074</v>
       </c>
       <c r="O19">
-        <v>4.72111164</v>
+        <v>4.6716222</v>
       </c>
       <c r="P19">
-        <v>11.01592716</v>
+        <v>10.9004518</v>
       </c>
       <c r="Q19">
-        <v>-6.48407284</v>
+        <v>-6.599548200000001</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.06681197258178177</v>
+        <v>0.06700098258984222</v>
       </c>
       <c r="T19">
-        <v>0.4852649556993481</v>
+        <v>0.4896300829062865</v>
       </c>
       <c r="U19">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V19">
         <v>0.3</v>
       </c>
       <c r="W19">
-        <v>0.03625999999999999</v>
+        <v>0.03745</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y19">
-        <v>9.926480514715808</v>
+        <v>9.077111880850197</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -3017,22 +3017,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.06168180572367062</v>
+        <v>0.06154317420446236</v>
       </c>
       <c r="C20">
-        <v>155.6017031850347</v>
+        <v>154.0064250819981</v>
       </c>
       <c r="D20">
-        <v>189.0977031850347</v>
+        <v>189.5044250819981</v>
       </c>
       <c r="E20">
-        <v>-34.364</v>
+        <v>-32.362</v>
       </c>
       <c r="F20">
-        <v>36.036</v>
+        <v>38.038</v>
       </c>
       <c r="G20">
         <v>2.54</v>
@@ -3053,28 +3053,28 @@
         <v>17.5</v>
       </c>
       <c r="M20">
-        <v>1.927926</v>
+        <v>2.035033</v>
       </c>
       <c r="N20">
-        <v>15.572074</v>
+        <v>15.464967</v>
       </c>
       <c r="O20">
-        <v>4.6716222</v>
+        <v>4.6394901</v>
       </c>
       <c r="P20">
-        <v>10.9004518</v>
+        <v>10.8254769</v>
       </c>
       <c r="Q20">
-        <v>-6.599548199999999</v>
+        <v>-6.6745231</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.06700098258984222</v>
+        <v>0.06719465951168192</v>
       </c>
       <c r="T20">
-        <v>0.4896300829062865</v>
+        <v>0.4941029910319149</v>
       </c>
       <c r="U20">
         <v>0.0535</v>
@@ -3091,7 +3091,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>9.077111880850198</v>
+        <v>8.599369150279134</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -3099,22 +3099,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.06154317420446236</v>
+        <v>0.0614045426852541</v>
       </c>
       <c r="C21">
-        <v>154.0064250819981</v>
+        <v>152.4129003505359</v>
       </c>
       <c r="D21">
-        <v>189.5044250819981</v>
+        <v>189.9129003505359</v>
       </c>
       <c r="E21">
-        <v>-32.362</v>
+        <v>-30.36</v>
       </c>
       <c r="F21">
-        <v>38.038</v>
+        <v>40.04000000000001</v>
       </c>
       <c r="G21">
         <v>2.54</v>
@@ -3135,28 +3135,28 @@
         <v>17.5</v>
       </c>
       <c r="M21">
-        <v>2.035033</v>
+        <v>2.14214</v>
       </c>
       <c r="N21">
-        <v>15.464967</v>
+        <v>15.35786</v>
       </c>
       <c r="O21">
-        <v>4.6394901</v>
+        <v>4.607358</v>
       </c>
       <c r="P21">
-        <v>10.8254769</v>
+        <v>10.750502</v>
       </c>
       <c r="Q21">
-        <v>-6.6745231</v>
+        <v>-6.749498000000001</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.06719465951168192</v>
+        <v>0.06739317835656762</v>
       </c>
       <c r="T21">
-        <v>0.4941029910319149</v>
+        <v>0.4986877218606841</v>
       </c>
       <c r="U21">
         <v>0.0535</v>
@@ -3173,7 +3173,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>8.599369150279134</v>
+        <v>8.169400692765176</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3181,22 +3181,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.0614045426852541</v>
+        <v>0.06126591116604585</v>
       </c>
       <c r="C22">
-        <v>152.4129003505359</v>
+        <v>150.8211403532752</v>
       </c>
       <c r="D22">
-        <v>189.9129003505359</v>
+        <v>190.3231403532752</v>
       </c>
       <c r="E22">
-        <v>-30.36</v>
+        <v>-28.358</v>
       </c>
       <c r="F22">
-        <v>40.04000000000001</v>
+        <v>42.04200000000001</v>
       </c>
       <c r="G22">
         <v>2.54</v>
@@ -3217,28 +3217,28 @@
         <v>17.5</v>
       </c>
       <c r="M22">
-        <v>2.14214</v>
+        <v>2.249247</v>
       </c>
       <c r="N22">
-        <v>15.35786</v>
+        <v>15.250753</v>
       </c>
       <c r="O22">
-        <v>4.607358</v>
+        <v>4.5752259</v>
       </c>
       <c r="P22">
-        <v>10.750502</v>
+        <v>10.6755271</v>
       </c>
       <c r="Q22">
-        <v>-6.749498000000001</v>
+        <v>-6.8244729</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.06739317835656762</v>
+        <v>0.06759672299499474</v>
       </c>
       <c r="T22">
-        <v>0.4986877218606841</v>
+        <v>0.5033885218243588</v>
       </c>
       <c r="U22">
         <v>0.0535</v>
@@ -3255,7 +3255,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>8.169400692765176</v>
+        <v>7.780381612157312</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3263,22 +3263,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.06126591116604585</v>
+        <v>0.06125047964683759</v>
       </c>
       <c r="C23">
-        <v>150.8211403532752</v>
+        <v>148.8649151343861</v>
       </c>
       <c r="D23">
-        <v>190.3231403532752</v>
+        <v>190.3689151343861</v>
       </c>
       <c r="E23">
-        <v>-28.358</v>
+        <v>-26.356</v>
       </c>
       <c r="F23">
-        <v>42.042</v>
+        <v>44.044</v>
       </c>
       <c r="G23">
         <v>2.54</v>
@@ -3299,45 +3299,45 @@
         <v>17.5</v>
       </c>
       <c r="M23">
-        <v>2.249247</v>
+        <v>2.3915892</v>
       </c>
       <c r="N23">
-        <v>15.250753</v>
+        <v>15.1084108</v>
       </c>
       <c r="O23">
-        <v>4.5752259</v>
+        <v>4.53252324</v>
       </c>
       <c r="P23">
-        <v>10.6755271</v>
+        <v>10.57588756</v>
       </c>
       <c r="Q23">
-        <v>-6.8244729</v>
+        <v>-6.92411244</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.06759672299499474</v>
+        <v>0.06780548672671485</v>
       </c>
       <c r="T23">
-        <v>0.5033885218243587</v>
+        <v>0.5082098551204353</v>
       </c>
       <c r="U23">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V23">
         <v>0.3</v>
       </c>
       <c r="W23">
-        <v>0.03745</v>
+        <v>0.03801</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y23">
-        <v>7.780381612157313</v>
+        <v>7.317310180193153</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3345,22 +3345,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.06125047964683759</v>
+        <v>0.06111744812762933</v>
       </c>
       <c r="C24">
-        <v>148.8649151343861</v>
+        <v>147.2584438134383</v>
       </c>
       <c r="D24">
-        <v>190.3689151343861</v>
+        <v>190.7644438134383</v>
       </c>
       <c r="E24">
-        <v>-26.356</v>
+        <v>-24.354</v>
       </c>
       <c r="F24">
-        <v>44.044</v>
+        <v>46.04600000000001</v>
       </c>
       <c r="G24">
         <v>2.54</v>
@@ -3381,28 +3381,28 @@
         <v>17.5</v>
       </c>
       <c r="M24">
-        <v>2.3915892</v>
+        <v>2.5002978</v>
       </c>
       <c r="N24">
-        <v>15.1084108</v>
+        <v>14.9997022</v>
       </c>
       <c r="O24">
-        <v>4.53252324</v>
+        <v>4.499910659999999</v>
       </c>
       <c r="P24">
-        <v>10.57588756</v>
+        <v>10.49979154</v>
       </c>
       <c r="Q24">
-        <v>-6.92411244</v>
+        <v>-7.00020846</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.06780548672671485</v>
+        <v>0.0680196728930251</v>
       </c>
       <c r="T24">
-        <v>0.5082098551204353</v>
+        <v>0.5131564178527734</v>
       </c>
       <c r="U24">
         <v>0.0543</v>
@@ -3419,7 +3419,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>7.317310180193153</v>
+        <v>6.99916625931519</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3427,22 +3427,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.06111744812762933</v>
+        <v>0.06098441660842106</v>
       </c>
       <c r="C25">
-        <v>147.2584438134383</v>
+        <v>145.6536194909347</v>
       </c>
       <c r="D25">
-        <v>190.7644438134383</v>
+        <v>191.1616194909347</v>
       </c>
       <c r="E25">
-        <v>-24.354</v>
+        <v>-22.352</v>
       </c>
       <c r="F25">
-        <v>46.04600000000001</v>
+        <v>48.04800000000001</v>
       </c>
       <c r="G25">
         <v>2.54</v>
@@ -3463,28 +3463,28 @@
         <v>17.5</v>
       </c>
       <c r="M25">
-        <v>2.5002978</v>
+        <v>2.609006400000001</v>
       </c>
       <c r="N25">
-        <v>14.9997022</v>
+        <v>14.8909936</v>
       </c>
       <c r="O25">
-        <v>4.499910659999999</v>
+        <v>4.46729808</v>
       </c>
       <c r="P25">
-        <v>10.49979154</v>
+        <v>10.42369552</v>
       </c>
       <c r="Q25">
-        <v>-7.00020846</v>
+        <v>-7.076304480000001</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.0680196728930251</v>
+        <v>0.06823949553739614</v>
       </c>
       <c r="T25">
-        <v>0.5131564178527734</v>
+        <v>0.5182331532885944</v>
       </c>
       <c r="U25">
         <v>0.0543</v>
@@ -3501,7 +3501,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>6.99916625931519</v>
+        <v>6.707534331843723</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3509,22 +3509,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.06098441660842106</v>
+        <v>0.06085138508921281</v>
       </c>
       <c r="C26">
-        <v>145.6536194909347</v>
+        <v>144.0504524755966</v>
       </c>
       <c r="D26">
-        <v>191.1616194909347</v>
+        <v>191.5604524755966</v>
       </c>
       <c r="E26">
-        <v>-22.352</v>
+        <v>-20.35</v>
       </c>
       <c r="F26">
-        <v>48.048</v>
+        <v>50.05</v>
       </c>
       <c r="G26">
         <v>2.54</v>
@@ -3545,28 +3545,28 @@
         <v>17.5</v>
       </c>
       <c r="M26">
-        <v>2.6090064</v>
+        <v>2.717715</v>
       </c>
       <c r="N26">
-        <v>14.8909936</v>
+        <v>14.782285</v>
       </c>
       <c r="O26">
-        <v>4.46729808</v>
+        <v>4.4346855</v>
       </c>
       <c r="P26">
-        <v>10.42369552</v>
+        <v>10.3475995</v>
       </c>
       <c r="Q26">
-        <v>-7.076304480000001</v>
+        <v>-7.152400499999999</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.06823949553739614</v>
+        <v>0.06846518011895042</v>
       </c>
       <c r="T26">
-        <v>0.5182331532885944</v>
+        <v>0.5234452683360372</v>
       </c>
       <c r="U26">
         <v>0.0543</v>
@@ -3583,7 +3583,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>6.707534331843724</v>
+        <v>6.439232958569975</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3591,22 +3591,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.06085138508921281</v>
+        <v>0.06071835357000455</v>
       </c>
       <c r="C27">
-        <v>144.0504524755966</v>
+        <v>142.4489531623567</v>
       </c>
       <c r="D27">
-        <v>191.5604524755966</v>
+        <v>191.9609531623567</v>
       </c>
       <c r="E27">
-        <v>-20.35</v>
+        <v>-18.348</v>
       </c>
       <c r="F27">
-        <v>50.05</v>
+        <v>52.05200000000001</v>
       </c>
       <c r="G27">
         <v>2.54</v>
@@ -3627,28 +3627,28 @@
         <v>17.5</v>
       </c>
       <c r="M27">
-        <v>2.717715</v>
+        <v>2.8264236</v>
       </c>
       <c r="N27">
-        <v>14.782285</v>
+        <v>14.6735764</v>
       </c>
       <c r="O27">
-        <v>4.4346855</v>
+        <v>4.40207292</v>
       </c>
       <c r="P27">
-        <v>10.3475995</v>
+        <v>10.27150348</v>
       </c>
       <c r="Q27">
-        <v>-7.152400499999999</v>
+        <v>-7.22849652</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.06846518011895042</v>
+        <v>0.06869696428378994</v>
       </c>
       <c r="T27">
-        <v>0.5234452683360372</v>
+        <v>0.5287982513577351</v>
       </c>
       <c r="U27">
         <v>0.0543</v>
@@ -3665,7 +3665,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>6.439232958569975</v>
+        <v>6.191570152471129</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3673,22 +3673,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.06071835357000455</v>
+        <v>0.06077432205079629</v>
       </c>
       <c r="C28">
-        <v>142.4489531623567</v>
+        <v>140.2782522474161</v>
       </c>
       <c r="D28">
-        <v>191.9609531623567</v>
+        <v>191.7922522474161</v>
       </c>
       <c r="E28">
-        <v>-18.348</v>
+        <v>-16.346</v>
       </c>
       <c r="F28">
-        <v>52.05200000000001</v>
+        <v>54.05400000000001</v>
       </c>
       <c r="G28">
         <v>2.54</v>
@@ -3709,45 +3709,45 @@
         <v>17.5</v>
       </c>
       <c r="M28">
-        <v>2.8264236</v>
+        <v>2.989186200000001</v>
       </c>
       <c r="N28">
-        <v>14.6735764</v>
+        <v>14.5108138</v>
       </c>
       <c r="O28">
-        <v>4.40207292</v>
+        <v>4.353244139999999</v>
       </c>
       <c r="P28">
-        <v>10.27150348</v>
+        <v>10.15756966</v>
       </c>
       <c r="Q28">
-        <v>-7.22849652</v>
+        <v>-7.34243034</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.06869696428378994</v>
+        <v>0.06893509869972095</v>
       </c>
       <c r="T28">
-        <v>0.5287982513577351</v>
+        <v>0.5342978914485208</v>
       </c>
       <c r="U28">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V28">
         <v>0.3</v>
       </c>
       <c r="W28">
-        <v>0.03801</v>
+        <v>0.03871</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y28">
-        <v>6.191570152471129</v>
+        <v>5.854436234183068</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3755,22 +3755,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.06077432205079629</v>
+        <v>0.06064829053158804</v>
       </c>
       <c r="C29">
-        <v>140.2782522474161</v>
+        <v>138.6565568325049</v>
       </c>
       <c r="D29">
-        <v>191.7922522474161</v>
+        <v>192.1725568325049</v>
       </c>
       <c r="E29">
-        <v>-16.346</v>
+        <v>-14.34399999999999</v>
       </c>
       <c r="F29">
-        <v>54.05400000000001</v>
+        <v>56.05600000000001</v>
       </c>
       <c r="G29">
         <v>2.54</v>
@@ -3791,28 +3791,28 @@
         <v>17.5</v>
       </c>
       <c r="M29">
-        <v>2.989186200000001</v>
+        <v>3.099896800000001</v>
       </c>
       <c r="N29">
-        <v>14.5108138</v>
+        <v>14.4001032</v>
       </c>
       <c r="O29">
-        <v>4.353244139999999</v>
+        <v>4.32003096</v>
       </c>
       <c r="P29">
-        <v>10.15756966</v>
+        <v>10.08007224</v>
       </c>
       <c r="Q29">
-        <v>-7.34243034</v>
+        <v>-7.41992776</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.06893509869972095</v>
+        <v>0.06917984796053894</v>
       </c>
       <c r="T29">
-        <v>0.5342978914485208</v>
+        <v>0.5399502993196059</v>
       </c>
       <c r="U29">
         <v>0.0553</v>
@@ -3829,7 +3829,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>5.854436234183068</v>
+        <v>5.645349225819388</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3837,22 +3837,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.06064829053158804</v>
+        <v>0.06052225901237979</v>
       </c>
       <c r="C30">
-        <v>138.6565568325049</v>
+        <v>137.03637262501</v>
       </c>
       <c r="D30">
-        <v>192.1725568325049</v>
+        <v>192.55437262501</v>
       </c>
       <c r="E30">
-        <v>-14.34399999999999</v>
+        <v>-12.34199999999999</v>
       </c>
       <c r="F30">
-        <v>56.05600000000001</v>
+        <v>58.05800000000001</v>
       </c>
       <c r="G30">
         <v>2.54</v>
@@ -3873,28 +3873,28 @@
         <v>17.5</v>
       </c>
       <c r="M30">
-        <v>3.099896800000001</v>
+        <v>3.210607400000001</v>
       </c>
       <c r="N30">
-        <v>14.4001032</v>
+        <v>14.2893926</v>
       </c>
       <c r="O30">
-        <v>4.32003096</v>
+        <v>4.28681778</v>
       </c>
       <c r="P30">
-        <v>10.08007224</v>
+        <v>10.00257482</v>
       </c>
       <c r="Q30">
-        <v>-7.41992776</v>
+        <v>-7.49742518</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.06917984796053894</v>
+        <v>0.06943149156673209</v>
       </c>
       <c r="T30">
-        <v>0.5399502993196059</v>
+        <v>0.5457619299476231</v>
       </c>
       <c r="U30">
         <v>0.0553</v>
@@ -3911,7 +3911,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>5.645349225819388</v>
+        <v>5.450682011135959</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3919,22 +3919,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.06052225901237979</v>
+        <v>0.06039622749317151</v>
       </c>
       <c r="C31">
-        <v>137.03637262501</v>
+        <v>135.417708650438</v>
       </c>
       <c r="D31">
-        <v>192.55437262501</v>
+        <v>192.937708650438</v>
       </c>
       <c r="E31">
-        <v>-12.34200000000001</v>
+        <v>-10.34</v>
       </c>
       <c r="F31">
-        <v>58.058</v>
+        <v>60.06</v>
       </c>
       <c r="G31">
         <v>2.54</v>
@@ -3955,28 +3955,28 @@
         <v>17.5</v>
       </c>
       <c r="M31">
-        <v>3.2106074</v>
+        <v>3.321318</v>
       </c>
       <c r="N31">
-        <v>14.2893926</v>
+        <v>14.178682</v>
       </c>
       <c r="O31">
-        <v>4.28681778</v>
+        <v>4.2536046</v>
       </c>
       <c r="P31">
-        <v>10.00257482</v>
+        <v>9.925077399999999</v>
       </c>
       <c r="Q31">
-        <v>-7.49742518</v>
+        <v>-7.574922600000001</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.06943149156673209</v>
+        <v>0.06969032499024502</v>
       </c>
       <c r="T31">
-        <v>0.5457619299476231</v>
+        <v>0.5517396071650121</v>
       </c>
       <c r="U31">
         <v>0.0553</v>
@@ -3993,7 +3993,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>5.450682011135961</v>
+        <v>5.268992610764762</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -4001,22 +4001,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.06039622749317151</v>
+        <v>0.06027019597396326</v>
       </c>
       <c r="C32">
-        <v>135.417708650438</v>
+        <v>133.8005740063102</v>
       </c>
       <c r="D32">
-        <v>192.937708650438</v>
+        <v>193.3225740063102</v>
       </c>
       <c r="E32">
-        <v>-10.34</v>
+        <v>-8.338000000000001</v>
       </c>
       <c r="F32">
-        <v>60.06</v>
+        <v>62.062</v>
       </c>
       <c r="G32">
         <v>2.54</v>
@@ -4037,28 +4037,28 @@
         <v>17.5</v>
       </c>
       <c r="M32">
-        <v>3.321318</v>
+        <v>3.4320286</v>
       </c>
       <c r="N32">
-        <v>14.178682</v>
+        <v>14.0679714</v>
       </c>
       <c r="O32">
-        <v>4.2536046</v>
+        <v>4.220391419999999</v>
       </c>
       <c r="P32">
-        <v>9.925077399999999</v>
+        <v>9.847579979999999</v>
       </c>
       <c r="Q32">
-        <v>-7.574922600000001</v>
+        <v>-7.652420020000001</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.06969032499024502</v>
+        <v>0.06995666083183082</v>
       </c>
       <c r="T32">
-        <v>0.5517396071650121</v>
+        <v>0.5578905503887023</v>
       </c>
       <c r="U32">
         <v>0.0553</v>
@@ -4075,7 +4075,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>5.268992610764762</v>
+        <v>5.099025107191705</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -4083,22 +4083,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.06027019597396326</v>
+        <v>0.060144164454755</v>
       </c>
       <c r="C33">
-        <v>133.8005740063102</v>
+        <v>132.1849778628829</v>
       </c>
       <c r="D33">
-        <v>193.3225740063102</v>
+        <v>193.7089778628829</v>
       </c>
       <c r="E33">
-        <v>-8.338000000000001</v>
+        <v>-6.335999999999999</v>
       </c>
       <c r="F33">
-        <v>62.062</v>
+        <v>64.06400000000001</v>
       </c>
       <c r="G33">
         <v>2.54</v>
@@ -4119,28 +4119,28 @@
         <v>17.5</v>
       </c>
       <c r="M33">
-        <v>3.4320286</v>
+        <v>3.542739200000001</v>
       </c>
       <c r="N33">
-        <v>14.0679714</v>
+        <v>13.9572608</v>
       </c>
       <c r="O33">
-        <v>4.220391419999999</v>
+        <v>4.18717824</v>
       </c>
       <c r="P33">
-        <v>9.847579979999999</v>
+        <v>9.770082560000001</v>
       </c>
       <c r="Q33">
-        <v>-7.652420020000001</v>
+        <v>-7.729917439999999</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.06995666083183082</v>
+        <v>0.07023083008052207</v>
       </c>
       <c r="T33">
-        <v>0.5578905503887023</v>
+        <v>0.564222403707207</v>
       </c>
       <c r="U33">
         <v>0.0553</v>
@@ -4157,7 +4157,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>5.099025107191705</v>
+        <v>4.939680572591964</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4165,22 +4165,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.060144164454755</v>
+        <v>0.06001813293554675</v>
       </c>
       <c r="C34">
-        <v>132.1849778628829</v>
+        <v>130.5709294638756</v>
       </c>
       <c r="D34">
-        <v>193.7089778628829</v>
+        <v>194.0969294638756</v>
       </c>
       <c r="E34">
-        <v>-6.335999999999999</v>
+        <v>-4.334000000000003</v>
       </c>
       <c r="F34">
-        <v>64.06400000000001</v>
+        <v>66.066</v>
       </c>
       <c r="G34">
         <v>2.54</v>
@@ -4201,28 +4201,28 @@
         <v>17.5</v>
       </c>
       <c r="M34">
-        <v>3.542739200000001</v>
+        <v>3.6534498</v>
       </c>
       <c r="N34">
-        <v>13.9572608</v>
+        <v>13.8465502</v>
       </c>
       <c r="O34">
-        <v>4.18717824</v>
+        <v>4.15396506</v>
       </c>
       <c r="P34">
-        <v>9.770082560000001</v>
+        <v>9.692585139999998</v>
       </c>
       <c r="Q34">
-        <v>-7.729917439999999</v>
+        <v>-7.807414860000002</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.07023083008052207</v>
+        <v>0.07051318348589067</v>
       </c>
       <c r="T34">
-        <v>0.564222403707207</v>
+        <v>0.5707432675725327</v>
       </c>
       <c r="U34">
         <v>0.0553</v>
@@ -4239,7 +4239,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>4.939680572591964</v>
+        <v>4.78999328251342</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4247,22 +4247,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.06001813293554675</v>
+        <v>0.05989210141633849</v>
       </c>
       <c r="C35">
-        <v>130.5709294638756</v>
+        <v>128.9584381272078</v>
       </c>
       <c r="D35">
-        <v>194.0969294638756</v>
+        <v>194.4864381272078</v>
       </c>
       <c r="E35">
-        <v>-4.334000000000003</v>
+        <v>-2.331999999999994</v>
       </c>
       <c r="F35">
-        <v>66.066</v>
+        <v>68.06800000000001</v>
       </c>
       <c r="G35">
         <v>2.54</v>
@@ -4283,28 +4283,28 @@
         <v>17.5</v>
       </c>
       <c r="M35">
-        <v>3.6534498</v>
+        <v>3.764160400000001</v>
       </c>
       <c r="N35">
-        <v>13.8465502</v>
+        <v>13.7358396</v>
       </c>
       <c r="O35">
-        <v>4.15396506</v>
+        <v>4.120751879999999</v>
       </c>
       <c r="P35">
-        <v>9.692585139999998</v>
+        <v>9.615087719999998</v>
       </c>
       <c r="Q35">
-        <v>-7.807414860000002</v>
+        <v>-7.884912280000002</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.07051318348589067</v>
+        <v>0.07080409305505832</v>
       </c>
       <c r="T35">
-        <v>0.5707432675725327</v>
+        <v>0.5774617333731712</v>
       </c>
       <c r="U35">
         <v>0.0553</v>
@@ -4321,7 +4321,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>4.78999328251342</v>
+        <v>4.649111127145378</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4329,22 +4329,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.05989210141633849</v>
+        <v>0.05976606989713022</v>
       </c>
       <c r="C36">
-        <v>128.9584381272078</v>
+        <v>127.3475132457452</v>
       </c>
       <c r="D36">
-        <v>194.4864381272078</v>
+        <v>194.8775132457453</v>
       </c>
       <c r="E36">
-        <v>-2.331999999999994</v>
+        <v>-0.3299999999999983</v>
       </c>
       <c r="F36">
-        <v>68.06800000000001</v>
+        <v>70.07000000000001</v>
       </c>
       <c r="G36">
         <v>2.54</v>
@@ -4365,28 +4365,28 @@
         <v>17.5</v>
       </c>
       <c r="M36">
-        <v>3.764160400000001</v>
+        <v>3.874871000000001</v>
       </c>
       <c r="N36">
-        <v>13.7358396</v>
+        <v>13.625129</v>
       </c>
       <c r="O36">
-        <v>4.120751879999999</v>
+        <v>4.0875387</v>
       </c>
       <c r="P36">
-        <v>9.615087719999998</v>
+        <v>9.5375903</v>
       </c>
       <c r="Q36">
-        <v>-7.884912280000002</v>
+        <v>-7.9624097</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.07080409305505832</v>
+        <v>0.07110395368789266</v>
       </c>
       <c r="T36">
-        <v>0.5774617333731712</v>
+        <v>0.5843869211984448</v>
       </c>
       <c r="U36">
         <v>0.0553</v>
@@ -4403,7 +4403,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>4.649111127145378</v>
+        <v>4.51627938065551</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4411,22 +4411,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.05976606989713022</v>
+        <v>0.06027003837792197</v>
       </c>
       <c r="C37">
-        <v>127.3475132457452</v>
+        <v>123.7910562221675</v>
       </c>
       <c r="D37">
-        <v>194.8775132457453</v>
+        <v>193.3230562221676</v>
       </c>
       <c r="E37">
-        <v>-0.3299999999999983</v>
+        <v>1.672000000000011</v>
       </c>
       <c r="F37">
-        <v>70.07000000000001</v>
+        <v>72.07200000000002</v>
       </c>
       <c r="G37">
         <v>2.54</v>
@@ -4447,45 +4447,45 @@
         <v>17.5</v>
       </c>
       <c r="M37">
-        <v>3.874871000000001</v>
+        <v>4.165761600000002</v>
       </c>
       <c r="N37">
-        <v>13.625129</v>
+        <v>13.3342384</v>
       </c>
       <c r="O37">
-        <v>4.0875387</v>
+        <v>4.000271519999999</v>
       </c>
       <c r="P37">
-        <v>9.5375903</v>
+        <v>9.333966879999998</v>
       </c>
       <c r="Q37">
-        <v>-7.9624097</v>
+        <v>-8.166033120000002</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.07110395368789266</v>
+        <v>0.07141318496550308</v>
       </c>
       <c r="T37">
-        <v>0.5843869211984448</v>
+        <v>0.5915285211432583</v>
       </c>
       <c r="U37">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V37">
         <v>0.3</v>
       </c>
       <c r="W37">
-        <v>0.03871</v>
+        <v>0.04046</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y37">
-        <v>4.51627938065551</v>
+        <v>4.200912505410773</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4493,22 +4493,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.06027003837792198</v>
+        <v>0.06016150685871372</v>
       </c>
       <c r="C38">
-        <v>123.7910562221675</v>
+        <v>122.1217156348591</v>
       </c>
       <c r="D38">
-        <v>193.3230562221675</v>
+        <v>193.6557156348591</v>
       </c>
       <c r="E38">
-        <v>1.671999999999997</v>
+        <v>3.674000000000007</v>
       </c>
       <c r="F38">
-        <v>72.072</v>
+        <v>74.07400000000001</v>
       </c>
       <c r="G38">
         <v>2.54</v>
@@ -4529,28 +4529,28 @@
         <v>17.5</v>
       </c>
       <c r="M38">
-        <v>4.165761600000001</v>
+        <v>4.281477200000001</v>
       </c>
       <c r="N38">
-        <v>13.3342384</v>
+        <v>13.2185228</v>
       </c>
       <c r="O38">
-        <v>4.00027152</v>
+        <v>3.96555684</v>
       </c>
       <c r="P38">
-        <v>9.33396688</v>
+        <v>9.252965959999999</v>
       </c>
       <c r="Q38">
-        <v>-8.16603312</v>
+        <v>-8.247034040000001</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.07141318496550308</v>
+        <v>0.0717322331090694</v>
       </c>
       <c r="T38">
-        <v>0.5915285211432583</v>
+        <v>0.5988968385466371</v>
       </c>
       <c r="U38">
         <v>0.0578</v>
@@ -4567,7 +4567,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>4.200912505410775</v>
+        <v>4.087374329588862</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4575,22 +4575,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.06016150685871372</v>
+        <v>0.06098397533950546</v>
       </c>
       <c r="C39">
-        <v>122.1217156348591</v>
+        <v>117.626939684767</v>
       </c>
       <c r="D39">
-        <v>193.6557156348591</v>
+        <v>191.1629396847671</v>
       </c>
       <c r="E39">
-        <v>3.674000000000007</v>
+        <v>5.676000000000002</v>
       </c>
       <c r="F39">
-        <v>74.07400000000001</v>
+        <v>76.07600000000001</v>
       </c>
       <c r="G39">
         <v>2.54</v>
@@ -4611,45 +4611,45 @@
         <v>17.5</v>
       </c>
       <c r="M39">
-        <v>4.281477200000001</v>
+        <v>4.663458800000001</v>
       </c>
       <c r="N39">
-        <v>13.2185228</v>
+        <v>12.8365412</v>
       </c>
       <c r="O39">
-        <v>3.96555684</v>
+        <v>3.85096236</v>
       </c>
       <c r="P39">
-        <v>9.252965959999999</v>
+        <v>8.985578839999999</v>
       </c>
       <c r="Q39">
-        <v>-8.247034040000001</v>
+        <v>-8.514421160000001</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.0717322331090694</v>
+        <v>0.07206157312823461</v>
       </c>
       <c r="T39">
-        <v>0.5988968385466371</v>
+        <v>0.6065028436081895</v>
       </c>
       <c r="U39">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V39">
         <v>0.3</v>
       </c>
       <c r="W39">
-        <v>0.04046</v>
+        <v>0.04291</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y39">
-        <v>4.087374329588862</v>
+        <v>3.752579523164222</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4657,22 +4657,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.06098397533950546</v>
+        <v>0.0608999438202972</v>
       </c>
       <c r="C40">
-        <v>117.626939684767</v>
+        <v>115.8766790412562</v>
       </c>
       <c r="D40">
-        <v>191.1629396847671</v>
+        <v>191.4146790412562</v>
       </c>
       <c r="E40">
-        <v>5.676000000000002</v>
+        <v>7.677999999999997</v>
       </c>
       <c r="F40">
-        <v>76.07600000000001</v>
+        <v>78.078</v>
       </c>
       <c r="G40">
         <v>2.54</v>
@@ -4693,28 +4693,28 @@
         <v>17.5</v>
       </c>
       <c r="M40">
-        <v>4.663458800000001</v>
+        <v>4.7861814</v>
       </c>
       <c r="N40">
-        <v>12.8365412</v>
+        <v>12.7138186</v>
       </c>
       <c r="O40">
-        <v>3.85096236</v>
+        <v>3.81414558</v>
       </c>
       <c r="P40">
-        <v>8.985578839999999</v>
+        <v>8.89967302</v>
       </c>
       <c r="Q40">
-        <v>-8.514421160000001</v>
+        <v>-8.60032698</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.07206157312823461</v>
+        <v>0.07240171118081508</v>
       </c>
       <c r="T40">
-        <v>0.6065028436081895</v>
+        <v>0.6143582258848748</v>
       </c>
       <c r="U40">
         <v>0.0613</v>
@@ -4731,7 +4731,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>3.752579523164222</v>
+        <v>3.656359535390781</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4739,22 +4739,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.0608999438202972</v>
+        <v>0.06081591230108894</v>
       </c>
       <c r="C41">
-        <v>115.8766790412562</v>
+        <v>114.1270822949236</v>
       </c>
       <c r="D41">
-        <v>191.4146790412562</v>
+        <v>191.6670822949236</v>
       </c>
       <c r="E41">
-        <v>7.677999999999997</v>
+        <v>9.680000000000007</v>
       </c>
       <c r="F41">
-        <v>78.078</v>
+        <v>80.08000000000001</v>
       </c>
       <c r="G41">
         <v>2.54</v>
@@ -4775,28 +4775,28 @@
         <v>17.5</v>
       </c>
       <c r="M41">
-        <v>4.7861814</v>
+        <v>4.908904000000001</v>
       </c>
       <c r="N41">
-        <v>12.7138186</v>
+        <v>12.591096</v>
       </c>
       <c r="O41">
-        <v>3.81414558</v>
+        <v>3.7773288</v>
       </c>
       <c r="P41">
-        <v>8.89967302</v>
+        <v>8.813767200000001</v>
       </c>
       <c r="Q41">
-        <v>-8.60032698</v>
+        <v>-8.686232799999999</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.07240171118081508</v>
+        <v>0.07275318716848157</v>
       </c>
       <c r="T41">
-        <v>0.6143582258848748</v>
+        <v>0.6224754542374497</v>
       </c>
       <c r="U41">
         <v>0.0613</v>
@@ -4813,7 +4813,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>3.656359535390781</v>
+        <v>3.564950547006012</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4821,22 +4821,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.06081591230108894</v>
+        <v>0.06153548078188068</v>
       </c>
       <c r="C42">
-        <v>114.1270822949236</v>
+        <v>109.9850475562802</v>
       </c>
       <c r="D42">
-        <v>191.6670822949236</v>
+        <v>189.5270475562803</v>
       </c>
       <c r="E42">
-        <v>9.680000000000007</v>
+        <v>11.682</v>
       </c>
       <c r="F42">
-        <v>80.08000000000001</v>
+        <v>82.08200000000001</v>
       </c>
       <c r="G42">
         <v>2.54</v>
@@ -4857,45 +4857,45 @@
         <v>17.5</v>
       </c>
       <c r="M42">
-        <v>4.908904000000001</v>
+        <v>5.2614562</v>
       </c>
       <c r="N42">
-        <v>12.591096</v>
+        <v>12.2385438</v>
       </c>
       <c r="O42">
-        <v>3.7773288</v>
+        <v>3.67156314</v>
       </c>
       <c r="P42">
-        <v>8.813767200000001</v>
+        <v>8.566980659999999</v>
       </c>
       <c r="Q42">
-        <v>-8.686232799999999</v>
+        <v>-8.933019340000001</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.07275318716848157</v>
+        <v>0.07311657759640794</v>
       </c>
       <c r="T42">
-        <v>0.6224754542374497</v>
+        <v>0.6308678428731626</v>
       </c>
       <c r="U42">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V42">
         <v>0.3</v>
       </c>
       <c r="W42">
-        <v>0.04291</v>
+        <v>0.04487</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y42">
-        <v>3.564950547006012</v>
+        <v>3.326075393348328</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4903,22 +4903,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.06153548078188068</v>
+        <v>0.06147104926267243</v>
       </c>
       <c r="C43">
-        <v>109.9850475562802</v>
+        <v>108.1727203931096</v>
       </c>
       <c r="D43">
-        <v>189.5270475562803</v>
+        <v>189.7167203931096</v>
       </c>
       <c r="E43">
-        <v>11.682</v>
+        <v>13.68400000000001</v>
       </c>
       <c r="F43">
-        <v>82.08200000000001</v>
+        <v>84.08400000000002</v>
       </c>
       <c r="G43">
         <v>2.54</v>
@@ -4939,28 +4939,28 @@
         <v>17.5</v>
       </c>
       <c r="M43">
-        <v>5.2614562</v>
+        <v>5.389784400000002</v>
       </c>
       <c r="N43">
-        <v>12.2385438</v>
+        <v>12.1102156</v>
       </c>
       <c r="O43">
-        <v>3.67156314</v>
+        <v>3.633064679999999</v>
       </c>
       <c r="P43">
-        <v>8.566980659999999</v>
+        <v>8.47715092</v>
       </c>
       <c r="Q43">
-        <v>-8.933019340000001</v>
+        <v>-9.02284908</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.07311657759640794</v>
+        <v>0.07349249872874557</v>
       </c>
       <c r="T43">
-        <v>0.6308678428731626</v>
+        <v>0.6395496242204517</v>
       </c>
       <c r="U43">
         <v>0.0641</v>
@@ -4977,7 +4977,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>3.326075393348328</v>
+        <v>3.246883122078129</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4985,22 +4985,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.06147104926267243</v>
+        <v>0.06140661774346418</v>
       </c>
       <c r="C44">
-        <v>108.1727203931096</v>
+        <v>106.3607732477256</v>
       </c>
       <c r="D44">
-        <v>189.7167203931096</v>
+        <v>189.9067732477256</v>
       </c>
       <c r="E44">
-        <v>13.684</v>
+        <v>15.68600000000001</v>
       </c>
       <c r="F44">
-        <v>84.084</v>
+        <v>86.08600000000001</v>
       </c>
       <c r="G44">
         <v>2.54</v>
@@ -5021,28 +5021,28 @@
         <v>17.5</v>
       </c>
       <c r="M44">
-        <v>5.389784400000001</v>
+        <v>5.518112600000001</v>
       </c>
       <c r="N44">
-        <v>12.1102156</v>
+        <v>11.9818874</v>
       </c>
       <c r="O44">
-        <v>3.63306468</v>
+        <v>3.594566219999999</v>
       </c>
       <c r="P44">
-        <v>8.47715092</v>
+        <v>8.387321179999999</v>
       </c>
       <c r="Q44">
-        <v>-9.02284908</v>
+        <v>-9.112678820000001</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.07349249872874557</v>
+        <v>0.07388161007625293</v>
       </c>
       <c r="T44">
-        <v>0.6395496242204517</v>
+        <v>0.6485360294746634</v>
       </c>
       <c r="U44">
         <v>0.0641</v>
@@ -5059,7 +5059,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>3.246883122078129</v>
+        <v>3.171374212262358</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -5067,22 +5067,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.06140661774346418</v>
+        <v>0.06134218622425591</v>
       </c>
       <c r="C45">
-        <v>106.3607732477256</v>
+        <v>104.5492072633467</v>
       </c>
       <c r="D45">
-        <v>189.9067732477256</v>
+        <v>190.0972072633467</v>
       </c>
       <c r="E45">
-        <v>15.68600000000001</v>
+        <v>17.688</v>
       </c>
       <c r="F45">
-        <v>86.08600000000001</v>
+        <v>88.08800000000001</v>
       </c>
       <c r="G45">
         <v>2.54</v>
@@ -5103,28 +5103,28 @@
         <v>17.5</v>
       </c>
       <c r="M45">
-        <v>5.518112600000001</v>
+        <v>5.646440800000001</v>
       </c>
       <c r="N45">
-        <v>11.9818874</v>
+        <v>11.8535592</v>
       </c>
       <c r="O45">
-        <v>3.594566219999999</v>
+        <v>3.55606776</v>
       </c>
       <c r="P45">
-        <v>8.387321179999999</v>
+        <v>8.29749144</v>
       </c>
       <c r="Q45">
-        <v>-9.112678820000001</v>
+        <v>-9.20250856</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.07388161007625293</v>
+        <v>0.07428461825759984</v>
       </c>
       <c r="T45">
-        <v>0.6485360294746634</v>
+        <v>0.6578433777736682</v>
       </c>
       <c r="U45">
         <v>0.0641</v>
@@ -5141,7 +5141,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>3.171374212262358</v>
+        <v>3.099297525620033</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5149,22 +5149,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.06134218622425591</v>
+        <v>0.06127775470504766</v>
       </c>
       <c r="C46">
-        <v>104.5492072633467</v>
+        <v>102.7380235877816</v>
       </c>
       <c r="D46">
-        <v>190.0972072633467</v>
+        <v>190.2880235877817</v>
       </c>
       <c r="E46">
-        <v>17.688</v>
+        <v>19.69</v>
       </c>
       <c r="F46">
-        <v>88.08800000000001</v>
+        <v>90.09</v>
       </c>
       <c r="G46">
         <v>2.54</v>
@@ -5185,28 +5185,28 @@
         <v>17.5</v>
       </c>
       <c r="M46">
-        <v>5.646440800000001</v>
+        <v>5.774769000000001</v>
       </c>
       <c r="N46">
-        <v>11.8535592</v>
+        <v>11.725231</v>
       </c>
       <c r="O46">
-        <v>3.55606776</v>
+        <v>3.517569299999999</v>
       </c>
       <c r="P46">
-        <v>8.29749144</v>
+        <v>8.207661699999999</v>
       </c>
       <c r="Q46">
-        <v>-9.20250856</v>
+        <v>-9.292338300000001</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.07428461825759984</v>
+        <v>0.07470228128190483</v>
       </c>
       <c r="T46">
-        <v>0.6578433777736682</v>
+        <v>0.667489175101728</v>
       </c>
       <c r="U46">
         <v>0.0641</v>
@@ -5223,7 +5223,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>3.099297525620033</v>
+        <v>3.030424247272921</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5231,22 +5231,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.06127775470504766</v>
+        <v>0.06372492318583939</v>
       </c>
       <c r="C47">
-        <v>102.7380235877816</v>
+        <v>93.74779244250789</v>
       </c>
       <c r="D47">
-        <v>190.2880235877817</v>
+        <v>183.2997924425079</v>
       </c>
       <c r="E47">
-        <v>19.69</v>
+        <v>21.69200000000001</v>
       </c>
       <c r="F47">
-        <v>90.09</v>
+        <v>92.09200000000001</v>
       </c>
       <c r="G47">
         <v>2.54</v>
@@ -5267,45 +5267,45 @@
         <v>17.5</v>
       </c>
       <c r="M47">
-        <v>5.774769000000001</v>
+        <v>6.621414800000001</v>
       </c>
       <c r="N47">
-        <v>11.725231</v>
+        <v>10.8785852</v>
       </c>
       <c r="O47">
-        <v>3.517569299999999</v>
+        <v>3.26357556</v>
       </c>
       <c r="P47">
-        <v>8.207661699999999</v>
+        <v>7.61500964</v>
       </c>
       <c r="Q47">
-        <v>-9.292338300000001</v>
+        <v>-9.88499036</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.07470228128190483</v>
+        <v>0.07513541330710999</v>
       </c>
       <c r="T47">
-        <v>0.667489175101728</v>
+        <v>0.6774922241826786</v>
       </c>
       <c r="U47">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V47">
         <v>0.3</v>
       </c>
       <c r="W47">
-        <v>0.04487</v>
+        <v>0.05033</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y47">
-        <v>3.030424247272921</v>
+        <v>2.642939693190645</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5313,22 +5313,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.06372492318583939</v>
+        <v>0.06371509166663114</v>
       </c>
       <c r="C48">
-        <v>93.74779244250789</v>
+        <v>91.77284065825621</v>
       </c>
       <c r="D48">
-        <v>183.2997924425079</v>
+        <v>183.3268406582562</v>
       </c>
       <c r="E48">
-        <v>21.69200000000001</v>
+        <v>23.694</v>
       </c>
       <c r="F48">
-        <v>92.09200000000001</v>
+        <v>94.09400000000001</v>
       </c>
       <c r="G48">
         <v>2.54</v>
@@ -5349,28 +5349,28 @@
         <v>17.5</v>
       </c>
       <c r="M48">
-        <v>6.621414800000001</v>
+        <v>6.765358600000001</v>
       </c>
       <c r="N48">
-        <v>10.8785852</v>
+        <v>10.7346414</v>
       </c>
       <c r="O48">
-        <v>3.26357556</v>
+        <v>3.22039242</v>
       </c>
       <c r="P48">
-        <v>7.61500964</v>
+        <v>7.51424898</v>
       </c>
       <c r="Q48">
-        <v>-9.88499036</v>
+        <v>-9.98575102</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.07513541330710999</v>
+        <v>0.07558488993703988</v>
       </c>
       <c r="T48">
-        <v>0.6774922241826786</v>
+        <v>0.687872746813854</v>
       </c>
       <c r="U48">
         <v>0.07190000000000001</v>
@@ -5387,7 +5387,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>2.642939693190645</v>
+        <v>2.586706933761057</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5395,22 +5395,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.06371509166663114</v>
+        <v>0.06370526014742289</v>
       </c>
       <c r="C49">
-        <v>91.77284065825621</v>
+        <v>89.79789685779913</v>
       </c>
       <c r="D49">
-        <v>183.3268406582562</v>
+        <v>183.3538968577992</v>
       </c>
       <c r="E49">
-        <v>23.694</v>
+        <v>25.69600000000001</v>
       </c>
       <c r="F49">
-        <v>94.09400000000001</v>
+        <v>96.09600000000002</v>
       </c>
       <c r="G49">
         <v>2.54</v>
@@ -5431,28 +5431,28 @@
         <v>17.5</v>
       </c>
       <c r="M49">
-        <v>6.765358600000001</v>
+        <v>6.909302400000001</v>
       </c>
       <c r="N49">
-        <v>10.7346414</v>
+        <v>10.5906976</v>
       </c>
       <c r="O49">
-        <v>3.22039242</v>
+        <v>3.17720928</v>
       </c>
       <c r="P49">
-        <v>7.51424898</v>
+        <v>7.413488319999999</v>
       </c>
       <c r="Q49">
-        <v>-9.98575102</v>
+        <v>-10.08651168</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.07558488993703988</v>
+        <v>0.07605165412965939</v>
       </c>
       <c r="T49">
-        <v>0.687872746813854</v>
+        <v>0.6986525203154591</v>
       </c>
       <c r="U49">
         <v>0.07190000000000001</v>
@@ -5469,7 +5469,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>2.586706933761057</v>
+        <v>2.532817205974368</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5477,22 +5477,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.06370526014742288</v>
+        <v>0.06503312862821463</v>
       </c>
       <c r="C50">
-        <v>89.79789685779917</v>
+        <v>84.21251062056362</v>
       </c>
       <c r="D50">
-        <v>183.3538968577992</v>
+        <v>179.7705106205636</v>
       </c>
       <c r="E50">
-        <v>25.696</v>
+        <v>27.69800000000001</v>
       </c>
       <c r="F50">
-        <v>96.096</v>
+        <v>98.09800000000001</v>
       </c>
       <c r="G50">
         <v>2.54</v>
@@ -5513,45 +5513,45 @@
         <v>17.5</v>
       </c>
       <c r="M50">
-        <v>6.909302400000001</v>
+        <v>7.435828400000002</v>
       </c>
       <c r="N50">
-        <v>10.5906976</v>
+        <v>10.0641716</v>
       </c>
       <c r="O50">
-        <v>3.17720928</v>
+        <v>3.019251479999999</v>
       </c>
       <c r="P50">
-        <v>7.413488319999999</v>
+        <v>7.044920119999999</v>
       </c>
       <c r="Q50">
-        <v>-10.08651168</v>
+        <v>-10.45507988</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.07605165412965939</v>
+        <v>0.07653672280042083</v>
       </c>
       <c r="T50">
-        <v>0.6986525203154591</v>
+        <v>0.7098550300328135</v>
       </c>
       <c r="U50">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V50">
         <v>0.3</v>
       </c>
       <c r="W50">
-        <v>0.05033</v>
+        <v>0.05306</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y50">
-        <v>2.532817205974368</v>
+        <v>2.353470125803333</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5559,22 +5559,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.06503312862821463</v>
+        <v>0.06505059710900636</v>
       </c>
       <c r="C51">
-        <v>84.21251062056362</v>
+        <v>82.16430334528967</v>
       </c>
       <c r="D51">
-        <v>179.7705106205636</v>
+        <v>179.7243033452897</v>
       </c>
       <c r="E51">
-        <v>27.69800000000001</v>
+        <v>29.7</v>
       </c>
       <c r="F51">
-        <v>98.09800000000001</v>
+        <v>100.1</v>
       </c>
       <c r="G51">
         <v>2.54</v>
@@ -5595,28 +5595,28 @@
         <v>17.5</v>
       </c>
       <c r="M51">
-        <v>7.435828400000002</v>
+        <v>7.587580000000001</v>
       </c>
       <c r="N51">
-        <v>10.0641716</v>
+        <v>9.912419999999999</v>
       </c>
       <c r="O51">
-        <v>3.019251479999999</v>
+        <v>2.973726</v>
       </c>
       <c r="P51">
-        <v>7.044920119999999</v>
+        <v>6.938694</v>
       </c>
       <c r="Q51">
-        <v>-10.45507988</v>
+        <v>-10.561306</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.07653672280042083</v>
+        <v>0.07704119421801273</v>
       </c>
       <c r="T51">
-        <v>0.7098550300328135</v>
+        <v>0.721505640138862</v>
       </c>
       <c r="U51">
         <v>0.07580000000000001</v>
@@ -5633,7 +5633,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>2.353470125803333</v>
+        <v>2.306400723287267</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5641,22 +5641,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.06505059710900636</v>
+        <v>0.06506806558979811</v>
       </c>
       <c r="C52">
-        <v>82.16430334528967</v>
+        <v>80.11611981766626</v>
       </c>
       <c r="D52">
-        <v>179.7243033452897</v>
+        <v>179.6781198176663</v>
       </c>
       <c r="E52">
-        <v>29.7</v>
+        <v>31.702</v>
       </c>
       <c r="F52">
-        <v>100.1</v>
+        <v>102.102</v>
       </c>
       <c r="G52">
         <v>2.54</v>
@@ -5677,28 +5677,28 @@
         <v>17.5</v>
       </c>
       <c r="M52">
-        <v>7.587580000000001</v>
+        <v>7.739331600000001</v>
       </c>
       <c r="N52">
-        <v>9.912419999999999</v>
+        <v>9.7606684</v>
       </c>
       <c r="O52">
-        <v>2.973726</v>
+        <v>2.92820052</v>
       </c>
       <c r="P52">
-        <v>6.938694</v>
+        <v>6.83246788</v>
       </c>
       <c r="Q52">
-        <v>-10.561306</v>
+        <v>-10.66753212</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.07704119421801273</v>
+        <v>0.07756625630571043</v>
       </c>
       <c r="T52">
-        <v>0.721505640138862</v>
+        <v>0.7336317853512799</v>
       </c>
       <c r="U52">
         <v>0.07580000000000001</v>
@@ -5715,7 +5715,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>2.306400723287267</v>
+        <v>2.261177179693399</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5723,22 +5723,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.06506806558979811</v>
+        <v>0.06508553407058984</v>
       </c>
       <c r="C53">
-        <v>80.11611981766626</v>
+        <v>78.06796001939091</v>
       </c>
       <c r="D53">
-        <v>179.6781198176663</v>
+        <v>179.6319600193909</v>
       </c>
       <c r="E53">
-        <v>31.702</v>
+        <v>33.70400000000001</v>
       </c>
       <c r="F53">
-        <v>102.102</v>
+        <v>104.104</v>
       </c>
       <c r="G53">
         <v>2.54</v>
@@ -5759,28 +5759,28 @@
         <v>17.5</v>
       </c>
       <c r="M53">
-        <v>7.739331600000001</v>
+        <v>7.891083200000002</v>
       </c>
       <c r="N53">
-        <v>9.7606684</v>
+        <v>9.608916799999999</v>
       </c>
       <c r="O53">
-        <v>2.92820052</v>
+        <v>2.88267504</v>
       </c>
       <c r="P53">
-        <v>6.83246788</v>
+        <v>6.72624176</v>
       </c>
       <c r="Q53">
-        <v>-10.66753212</v>
+        <v>-10.77375824</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.07756625630571043</v>
+        <v>0.07811319598039551</v>
       </c>
       <c r="T53">
-        <v>0.7336317853512799</v>
+        <v>0.7462631866142151</v>
       </c>
       <c r="U53">
         <v>0.07580000000000001</v>
@@ -5797,7 +5797,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>2.261177179693399</v>
+        <v>2.217693003160833</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5805,22 +5805,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.06508553407058984</v>
+        <v>0.0651030025513816</v>
       </c>
       <c r="C54">
-        <v>78.06796001939091</v>
+        <v>76.01982393217976</v>
       </c>
       <c r="D54">
-        <v>179.6319600193909</v>
+        <v>179.5858239321798</v>
       </c>
       <c r="E54">
-        <v>33.70400000000001</v>
+        <v>35.706</v>
       </c>
       <c r="F54">
-        <v>104.104</v>
+        <v>106.106</v>
       </c>
       <c r="G54">
         <v>2.54</v>
@@ -5841,28 +5841,28 @@
         <v>17.5</v>
       </c>
       <c r="M54">
-        <v>7.891083200000002</v>
+        <v>8.042834800000001</v>
       </c>
       <c r="N54">
-        <v>9.608916799999999</v>
+        <v>9.457165199999999</v>
       </c>
       <c r="O54">
-        <v>2.88267504</v>
+        <v>2.837149559999999</v>
       </c>
       <c r="P54">
-        <v>6.72624176</v>
+        <v>6.620015639999999</v>
       </c>
       <c r="Q54">
-        <v>-10.77375824</v>
+        <v>-10.87998436</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.07811319598039551</v>
+        <v>0.07868340968379062</v>
       </c>
       <c r="T54">
-        <v>0.7462631866142151</v>
+        <v>0.759432094313871</v>
       </c>
       <c r="U54">
         <v>0.07580000000000001</v>
@@ -5879,7 +5879,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>2.217693003160833</v>
+        <v>2.175849738950252</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5887,22 +5887,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.0651030025513816</v>
+        <v>0.06512047103217335</v>
       </c>
       <c r="C55">
-        <v>76.01982393217976</v>
+        <v>73.97171153776806</v>
       </c>
       <c r="D55">
-        <v>179.5858239321798</v>
+        <v>179.5397115377681</v>
       </c>
       <c r="E55">
-        <v>35.706</v>
+        <v>37.70800000000001</v>
       </c>
       <c r="F55">
-        <v>106.106</v>
+        <v>108.108</v>
       </c>
       <c r="G55">
         <v>2.54</v>
@@ -5923,28 +5923,28 @@
         <v>17.5</v>
       </c>
       <c r="M55">
-        <v>8.042834800000001</v>
+        <v>8.194586400000002</v>
       </c>
       <c r="N55">
-        <v>9.457165199999999</v>
+        <v>9.305413599999998</v>
       </c>
       <c r="O55">
-        <v>2.837149559999999</v>
+        <v>2.791624079999999</v>
       </c>
       <c r="P55">
-        <v>6.620015639999999</v>
+        <v>6.513789519999999</v>
       </c>
       <c r="Q55">
-        <v>-10.87998436</v>
+        <v>-10.98621048</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.07868340968379062</v>
+        <v>0.07927841528733334</v>
       </c>
       <c r="T55">
-        <v>0.759432094313871</v>
+        <v>0.7731735632178598</v>
       </c>
       <c r="U55">
         <v>0.07580000000000001</v>
@@ -5961,7 +5961,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>2.175849738950252</v>
+        <v>2.135556225265987</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5969,22 +5969,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.06512047103217335</v>
+        <v>0.06513793951296508</v>
       </c>
       <c r="C56">
-        <v>73.97171153776806</v>
+        <v>71.92362281790966</v>
       </c>
       <c r="D56">
-        <v>179.5397115377681</v>
+        <v>179.4936228179097</v>
       </c>
       <c r="E56">
-        <v>37.70800000000001</v>
+        <v>39.71000000000001</v>
       </c>
       <c r="F56">
-        <v>108.108</v>
+        <v>110.11</v>
       </c>
       <c r="G56">
         <v>2.54</v>
@@ -6005,28 +6005,28 @@
         <v>17.5</v>
       </c>
       <c r="M56">
-        <v>8.194586400000002</v>
+        <v>8.346338000000001</v>
       </c>
       <c r="N56">
-        <v>9.305413599999998</v>
+        <v>9.153661999999999</v>
       </c>
       <c r="O56">
-        <v>2.791624079999999</v>
+        <v>2.746098599999999</v>
       </c>
       <c r="P56">
-        <v>6.513789519999999</v>
+        <v>6.407563399999999</v>
       </c>
       <c r="Q56">
-        <v>-10.98621048</v>
+        <v>-11.0924366</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.07927841528733334</v>
+        <v>0.07989986558436685</v>
       </c>
       <c r="T56">
-        <v>0.7731735632178598</v>
+        <v>0.787525764073137</v>
       </c>
       <c r="U56">
         <v>0.07580000000000001</v>
@@ -6043,7 +6043,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>2.135556225265987</v>
+        <v>2.096727930261151</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -6051,22 +6051,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.06513793951296508</v>
+        <v>0.06515540799375681</v>
       </c>
       <c r="C57">
-        <v>71.92362281790966</v>
+        <v>69.87555775437698</v>
       </c>
       <c r="D57">
-        <v>179.4936228179097</v>
+        <v>179.447557754377</v>
       </c>
       <c r="E57">
-        <v>39.71000000000001</v>
+        <v>41.71200000000002</v>
       </c>
       <c r="F57">
-        <v>110.11</v>
+        <v>112.112</v>
       </c>
       <c r="G57">
         <v>2.54</v>
@@ -6087,28 +6087,28 @@
         <v>17.5</v>
       </c>
       <c r="M57">
-        <v>8.346338000000001</v>
+        <v>8.498089600000002</v>
       </c>
       <c r="N57">
-        <v>9.153661999999999</v>
+        <v>9.001910399999998</v>
       </c>
       <c r="O57">
-        <v>2.746098599999999</v>
+        <v>2.700573119999999</v>
       </c>
       <c r="P57">
-        <v>6.407563399999999</v>
+        <v>6.301337279999998</v>
       </c>
       <c r="Q57">
-        <v>-11.0924366</v>
+        <v>-11.19866272</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.07989986558436685</v>
+        <v>0.08054956362217458</v>
       </c>
       <c r="T57">
-        <v>0.787525764073137</v>
+        <v>0.8025303376945632</v>
       </c>
       <c r="U57">
         <v>0.07580000000000001</v>
@@ -6125,7 +6125,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>2.096727930261151</v>
+        <v>2.059286360077916</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6133,22 +6133,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.06515540799375681</v>
+        <v>0.06517287647454856</v>
       </c>
       <c r="C58">
-        <v>69.87555775437698</v>
+        <v>67.82751632896135</v>
       </c>
       <c r="D58">
-        <v>179.447557754377</v>
+        <v>179.4015163289614</v>
       </c>
       <c r="E58">
-        <v>41.71200000000002</v>
+        <v>43.71400000000001</v>
       </c>
       <c r="F58">
-        <v>112.112</v>
+        <v>114.114</v>
       </c>
       <c r="G58">
         <v>2.54</v>
@@ -6169,28 +6169,28 @@
         <v>17.5</v>
       </c>
       <c r="M58">
-        <v>8.498089600000002</v>
+        <v>8.649841200000003</v>
       </c>
       <c r="N58">
-        <v>9.001910399999998</v>
+        <v>8.850158799999997</v>
       </c>
       <c r="O58">
-        <v>2.700573119999999</v>
+        <v>2.655047639999999</v>
       </c>
       <c r="P58">
-        <v>6.301337279999998</v>
+        <v>6.195111159999998</v>
       </c>
       <c r="Q58">
-        <v>-11.19866272</v>
+        <v>-11.30488884</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.08054956362217458</v>
+        <v>0.08122948017336876</v>
       </c>
       <c r="T58">
-        <v>0.8025303376945632</v>
+        <v>0.8182327984611719</v>
       </c>
       <c r="U58">
         <v>0.07580000000000001</v>
@@ -6207,7 +6207,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>2.059286360077916</v>
+        <v>2.023158529199356</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6215,22 +6215,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.06517287647454856</v>
+        <v>0.0709555449553403</v>
       </c>
       <c r="C59">
-        <v>67.82751632896135</v>
+        <v>51.78099511002303</v>
       </c>
       <c r="D59">
-        <v>179.4015163289614</v>
+        <v>165.3569951100231</v>
       </c>
       <c r="E59">
-        <v>43.71400000000001</v>
+        <v>45.71600000000002</v>
       </c>
       <c r="F59">
-        <v>114.114</v>
+        <v>116.116</v>
       </c>
       <c r="G59">
         <v>2.54</v>
@@ -6251,45 +6251,45 @@
         <v>17.5</v>
       </c>
       <c r="M59">
-        <v>8.649841200000003</v>
+        <v>10.45044</v>
       </c>
       <c r="N59">
-        <v>8.850158799999997</v>
+        <v>7.049559999999998</v>
       </c>
       <c r="O59">
-        <v>2.655047639999999</v>
+        <v>2.114867999999999</v>
       </c>
       <c r="P59">
-        <v>6.195111159999998</v>
+        <v>4.934691999999998</v>
       </c>
       <c r="Q59">
-        <v>-11.30488884</v>
+        <v>-12.565308</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.08122948017336876</v>
+        <v>0.0819417737031912</v>
       </c>
       <c r="T59">
-        <v>0.8182327984611719</v>
+        <v>0.834682995454762</v>
       </c>
       <c r="U59">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V59">
         <v>0.3</v>
       </c>
       <c r="W59">
-        <v>0.05306</v>
+        <v>0.063</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y59">
-        <v>2.023158529199356</v>
+        <v>1.674570640087881</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6297,22 +6297,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.0709555449553403</v>
+        <v>0.07107241343613205</v>
       </c>
       <c r="C60">
-        <v>51.78099511002306</v>
+        <v>49.51778744034893</v>
       </c>
       <c r="D60">
-        <v>165.3569951100231</v>
+        <v>165.0957874403489</v>
       </c>
       <c r="E60">
-        <v>45.71599999999999</v>
+        <v>47.718</v>
       </c>
       <c r="F60">
-        <v>116.116</v>
+        <v>118.118</v>
       </c>
       <c r="G60">
         <v>2.54</v>
@@ -6333,28 +6333,28 @@
         <v>17.5</v>
       </c>
       <c r="M60">
-        <v>10.45044</v>
+        <v>10.63062</v>
       </c>
       <c r="N60">
-        <v>7.04956</v>
+        <v>6.86938</v>
       </c>
       <c r="O60">
-        <v>2.114868</v>
+        <v>2.060814</v>
       </c>
       <c r="P60">
-        <v>4.934692</v>
+        <v>4.808566</v>
       </c>
       <c r="Q60">
-        <v>-12.565308</v>
+        <v>-12.691434</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.0819417737031912</v>
+        <v>0.08268881325885864</v>
       </c>
       <c r="T60">
-        <v>0.8346829954547618</v>
+        <v>0.8519356410821856</v>
       </c>
       <c r="U60">
         <v>0.09</v>
@@ -6371,7 +6371,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>1.674570640087881</v>
+        <v>1.646188086866053</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6379,22 +6379,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.07107241343613205</v>
+        <v>0.07118928191692378</v>
       </c>
       <c r="C61">
-        <v>49.51778744034893</v>
+        <v>47.25540370724156</v>
       </c>
       <c r="D61">
-        <v>165.0957874403489</v>
+        <v>164.8354037072416</v>
       </c>
       <c r="E61">
-        <v>47.718</v>
+        <v>49.72</v>
       </c>
       <c r="F61">
-        <v>118.118</v>
+        <v>120.12</v>
       </c>
       <c r="G61">
         <v>2.54</v>
@@ -6415,28 +6415,28 @@
         <v>17.5</v>
       </c>
       <c r="M61">
-        <v>10.63062</v>
+        <v>10.8108</v>
       </c>
       <c r="N61">
-        <v>6.86938</v>
+        <v>6.6892</v>
       </c>
       <c r="O61">
-        <v>2.060814</v>
+        <v>2.00676</v>
       </c>
       <c r="P61">
-        <v>4.808566</v>
+        <v>4.68244</v>
       </c>
       <c r="Q61">
-        <v>-12.691434</v>
+        <v>-12.81756</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.08268881325885864</v>
+        <v>0.08347320479230946</v>
       </c>
       <c r="T61">
-        <v>0.8519356410821856</v>
+        <v>0.8700509189909806</v>
       </c>
       <c r="U61">
         <v>0.09</v>
@@ -6453,7 +6453,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>1.646188086866053</v>
+        <v>1.618751618751619</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6461,22 +6461,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.07118928191692378</v>
+        <v>0.07130615039771553</v>
       </c>
       <c r="C62">
-        <v>47.25540370724156</v>
+        <v>44.99384001838155</v>
       </c>
       <c r="D62">
-        <v>164.8354037072416</v>
+        <v>164.5758400183816</v>
       </c>
       <c r="E62">
-        <v>49.72</v>
+        <v>51.72200000000001</v>
       </c>
       <c r="F62">
-        <v>120.12</v>
+        <v>122.122</v>
       </c>
       <c r="G62">
         <v>2.54</v>
@@ -6497,28 +6497,28 @@
         <v>17.5</v>
       </c>
       <c r="M62">
-        <v>10.8108</v>
+        <v>10.99098</v>
       </c>
       <c r="N62">
-        <v>6.6892</v>
+        <v>6.50902</v>
       </c>
       <c r="O62">
-        <v>2.00676</v>
+        <v>1.952706</v>
       </c>
       <c r="P62">
-        <v>4.68244</v>
+        <v>4.556314</v>
       </c>
       <c r="Q62">
-        <v>-12.81756</v>
+        <v>-12.943686</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.08347320479230946</v>
+        <v>0.08429782153260391</v>
       </c>
       <c r="T62">
-        <v>0.8700509189909806</v>
+        <v>0.8890951855104829</v>
       </c>
       <c r="U62">
         <v>0.09</v>
@@ -6535,7 +6535,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>1.618751618751619</v>
+        <v>1.592214706968805</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6543,22 +6543,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.07130615039771553</v>
+        <v>0.07142301887850727</v>
       </c>
       <c r="C63">
-        <v>44.99384001838155</v>
+        <v>42.73309250592756</v>
       </c>
       <c r="D63">
-        <v>164.5758400183816</v>
+        <v>164.3170925059276</v>
       </c>
       <c r="E63">
-        <v>51.72200000000001</v>
+        <v>53.724</v>
       </c>
       <c r="F63">
-        <v>122.122</v>
+        <v>124.124</v>
       </c>
       <c r="G63">
         <v>2.54</v>
@@ -6579,28 +6579,28 @@
         <v>17.5</v>
       </c>
       <c r="M63">
-        <v>10.99098</v>
+        <v>11.17116</v>
       </c>
       <c r="N63">
-        <v>6.50902</v>
+        <v>6.32884</v>
       </c>
       <c r="O63">
-        <v>1.952706</v>
+        <v>1.898652</v>
       </c>
       <c r="P63">
-        <v>4.556314</v>
+        <v>4.430187999999999</v>
       </c>
       <c r="Q63">
-        <v>-12.943686</v>
+        <v>-13.069812</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.08429782153260391</v>
+        <v>0.0851658391539665</v>
       </c>
       <c r="T63">
-        <v>0.8890951855104829</v>
+        <v>0.9091417818468013</v>
       </c>
       <c r="U63">
         <v>0.09</v>
@@ -6617,7 +6617,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>1.592214706968805</v>
+        <v>1.566533824598341</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6625,22 +6625,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.07142301887850727</v>
+        <v>0.07153988735929902</v>
       </c>
       <c r="C64">
-        <v>42.73309250592756</v>
+        <v>40.47315732632444</v>
       </c>
       <c r="D64">
-        <v>164.3170925059276</v>
+        <v>164.0591573263245</v>
       </c>
       <c r="E64">
-        <v>53.724</v>
+        <v>55.726</v>
       </c>
       <c r="F64">
-        <v>124.124</v>
+        <v>126.126</v>
       </c>
       <c r="G64">
         <v>2.54</v>
@@ -6661,28 +6661,28 @@
         <v>17.5</v>
       </c>
       <c r="M64">
-        <v>11.17116</v>
+        <v>11.35134</v>
       </c>
       <c r="N64">
-        <v>6.32884</v>
+        <v>6.14866</v>
       </c>
       <c r="O64">
-        <v>1.898652</v>
+        <v>1.844598</v>
       </c>
       <c r="P64">
-        <v>4.430187999999999</v>
+        <v>4.304062</v>
       </c>
       <c r="Q64">
-        <v>-13.069812</v>
+        <v>-13.195938</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.0851658391539665</v>
+        <v>0.08608077664675409</v>
       </c>
       <c r="T64">
-        <v>0.9091417818468013</v>
+        <v>0.9302719779850829</v>
       </c>
       <c r="U64">
         <v>0.09</v>
@@ -6699,7 +6699,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>1.566533824598341</v>
+        <v>1.541668208334875</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6707,22 +6707,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.07153988735929902</v>
+        <v>0.07165675584009076</v>
       </c>
       <c r="C65">
-        <v>40.47315732632444</v>
+        <v>38.21403066011257</v>
       </c>
       <c r="D65">
-        <v>164.0591573263245</v>
+        <v>163.8020306601126</v>
       </c>
       <c r="E65">
-        <v>55.726</v>
+        <v>57.72800000000001</v>
       </c>
       <c r="F65">
-        <v>126.126</v>
+        <v>128.128</v>
       </c>
       <c r="G65">
         <v>2.54</v>
@@ -6743,28 +6743,28 @@
         <v>17.5</v>
       </c>
       <c r="M65">
-        <v>11.35134</v>
+        <v>11.53152</v>
       </c>
       <c r="N65">
-        <v>6.14866</v>
+        <v>5.96848</v>
       </c>
       <c r="O65">
-        <v>1.844598</v>
+        <v>1.790544</v>
       </c>
       <c r="P65">
-        <v>4.304062</v>
+        <v>4.177936</v>
       </c>
       <c r="Q65">
-        <v>-13.195938</v>
+        <v>-13.322064</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.08608077664675409</v>
+        <v>0.08704654400025211</v>
       </c>
       <c r="T65">
-        <v>0.9302719779850829</v>
+        <v>0.9525760739088244</v>
       </c>
       <c r="U65">
         <v>0.09</v>
@@ -6781,7 +6781,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>1.541668208334875</v>
+        <v>1.517579642579642</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6789,22 +6789,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.07165675584009076</v>
+        <v>0.1003205707271277</v>
       </c>
       <c r="C66">
-        <v>38.21403066011257</v>
+        <v>-9.270117159737865</v>
       </c>
       <c r="D66">
-        <v>163.8020306601126</v>
+        <v>118.3198828402622</v>
       </c>
       <c r="E66">
-        <v>57.72800000000001</v>
+        <v>59.73000000000002</v>
       </c>
       <c r="F66">
-        <v>128.128</v>
+        <v>130.13</v>
       </c>
       <c r="G66">
         <v>2.54</v>
@@ -6825,45 +6825,45 @@
         <v>17.5</v>
       </c>
       <c r="M66">
-        <v>11.53152</v>
+        <v>19.10308400000001</v>
       </c>
       <c r="N66">
-        <v>5.96848</v>
+        <v>-1.603084000000006</v>
       </c>
       <c r="O66">
-        <v>1.790544</v>
+        <v>-0.4809252000000018</v>
       </c>
       <c r="P66">
-        <v>4.177936</v>
+        <v>-1.122158800000004</v>
       </c>
       <c r="Q66">
-        <v>-13.322064</v>
+        <v>-18.6221588</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.08704654400025211</v>
+        <v>0.08892670557401108</v>
       </c>
       <c r="T66">
-        <v>0.9525760739088244</v>
+        <v>0.9959978192612258</v>
       </c>
       <c r="U66">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V66">
-        <v>0.3</v>
+        <v>0.2748247351055986</v>
       </c>
       <c r="W66">
-        <v>0.063</v>
+        <v>0.1064557288864981</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y66">
-        <v>1.517579642579642</v>
+        <v>0.9160824503519952</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6871,22 +6871,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1003205707271277</v>
+        <v>0.1013305707271277</v>
       </c>
       <c r="C67">
-        <v>-9.270117159737865</v>
+        <v>-12.41852298619467</v>
       </c>
       <c r="D67">
-        <v>118.3198828402622</v>
+        <v>117.1734770138053</v>
       </c>
       <c r="E67">
-        <v>59.73000000000002</v>
+        <v>61.732</v>
       </c>
       <c r="F67">
-        <v>130.13</v>
+        <v>132.132</v>
       </c>
       <c r="G67">
         <v>2.54</v>
@@ -6907,37 +6907,37 @@
         <v>17.5</v>
       </c>
       <c r="M67">
-        <v>19.10308400000001</v>
+        <v>19.3969776</v>
       </c>
       <c r="N67">
-        <v>-1.603084000000006</v>
+        <v>-1.896977600000003</v>
       </c>
       <c r="O67">
-        <v>-0.4809252000000018</v>
+        <v>-0.5690932800000009</v>
       </c>
       <c r="P67">
-        <v>-1.122158800000004</v>
+        <v>-1.327884320000002</v>
       </c>
       <c r="Q67">
-        <v>-18.6221588</v>
+        <v>-18.82788432</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.08892670557401108</v>
+        <v>0.09019513809089376</v>
       </c>
       <c r="T67">
-        <v>0.9959978192612258</v>
+        <v>1.025291872768909</v>
       </c>
       <c r="U67">
         <v>0.1468</v>
       </c>
       <c r="V67">
-        <v>0.2748247351055986</v>
+        <v>0.270660723967635</v>
       </c>
       <c r="W67">
-        <v>0.1064557288864981</v>
+        <v>0.1070670057215512</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6945,7 +6945,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.9160824503519952</v>
+        <v>0.90220241322545</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6953,22 +6953,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1013305707271277</v>
+        <v>0.1023405707271277</v>
       </c>
       <c r="C68">
-        <v>-12.41852298619467</v>
+        <v>-15.54492685153589</v>
       </c>
       <c r="D68">
-        <v>117.1734770138053</v>
+        <v>116.0490731484641</v>
       </c>
       <c r="E68">
-        <v>61.732</v>
+        <v>63.73400000000001</v>
       </c>
       <c r="F68">
-        <v>132.132</v>
+        <v>134.134</v>
       </c>
       <c r="G68">
         <v>2.54</v>
@@ -6989,37 +6989,37 @@
         <v>17.5</v>
       </c>
       <c r="M68">
-        <v>19.3969776</v>
+        <v>19.6908712</v>
       </c>
       <c r="N68">
-        <v>-1.896977600000003</v>
+        <v>-2.190871200000004</v>
       </c>
       <c r="O68">
-        <v>-0.5690932800000009</v>
+        <v>-0.6572613600000011</v>
       </c>
       <c r="P68">
-        <v>-1.327884320000002</v>
+        <v>-1.533609840000003</v>
       </c>
       <c r="Q68">
-        <v>-18.82788432</v>
+        <v>-19.03360984</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.09019513809089376</v>
+        <v>0.09154044530576932</v>
       </c>
       <c r="T68">
-        <v>1.025291872768909</v>
+        <v>1.056361323458876</v>
       </c>
       <c r="U68">
         <v>0.1468</v>
       </c>
       <c r="V68">
-        <v>0.270660723967635</v>
+        <v>0.2666210116696106</v>
       </c>
       <c r="W68">
-        <v>0.1070670057215512</v>
+        <v>0.1076600354869012</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -7027,7 +7027,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.90220241322545</v>
+        <v>0.8887367055653687</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -7035,22 +7035,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1023405707271277</v>
+        <v>0.1033505707271277</v>
       </c>
       <c r="C69">
-        <v>-15.54492685153589</v>
+        <v>-18.64995613192266</v>
       </c>
       <c r="D69">
-        <v>116.0490731484641</v>
+        <v>114.9460438680774</v>
       </c>
       <c r="E69">
-        <v>63.73400000000001</v>
+        <v>65.73600000000002</v>
       </c>
       <c r="F69">
-        <v>134.134</v>
+        <v>136.136</v>
       </c>
       <c r="G69">
         <v>2.54</v>
@@ -7071,37 +7071,37 @@
         <v>17.5</v>
       </c>
       <c r="M69">
-        <v>19.6908712</v>
+        <v>19.9847648</v>
       </c>
       <c r="N69">
-        <v>-2.190871200000004</v>
+        <v>-2.484764800000004</v>
       </c>
       <c r="O69">
-        <v>-0.6572613600000011</v>
+        <v>-0.7454294400000012</v>
       </c>
       <c r="P69">
-        <v>-1.533609840000003</v>
+        <v>-1.739335360000003</v>
       </c>
       <c r="Q69">
-        <v>-19.03360984</v>
+        <v>-19.23933536</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.09154044530576932</v>
+        <v>0.09296983422157462</v>
       </c>
       <c r="T69">
-        <v>1.056361323458876</v>
+        <v>1.089372614816966</v>
       </c>
       <c r="U69">
         <v>0.1468</v>
       </c>
       <c r="V69">
-        <v>0.2666210116696106</v>
+        <v>0.2627001144391751</v>
       </c>
       <c r="W69">
-        <v>0.1076600354869012</v>
+        <v>0.1082356232003291</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -7109,7 +7109,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.8887367055653687</v>
+        <v>0.8756670481305837</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7117,22 +7117,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1033505707271277</v>
+        <v>0.1043605707271277</v>
       </c>
       <c r="C70">
-        <v>-18.64995613192266</v>
+        <v>-21.73421457562505</v>
       </c>
       <c r="D70">
-        <v>114.9460438680774</v>
+        <v>113.863785424375</v>
       </c>
       <c r="E70">
-        <v>65.73600000000002</v>
+        <v>67.73800000000003</v>
       </c>
       <c r="F70">
-        <v>136.136</v>
+        <v>138.138</v>
       </c>
       <c r="G70">
         <v>2.54</v>
@@ -7153,37 +7153,37 @@
         <v>17.5</v>
       </c>
       <c r="M70">
-        <v>19.9847648</v>
+        <v>20.27865840000001</v>
       </c>
       <c r="N70">
-        <v>-2.484764800000004</v>
+        <v>-2.778658400000008</v>
       </c>
       <c r="O70">
-        <v>-0.7454294400000012</v>
+        <v>-0.8335975200000024</v>
       </c>
       <c r="P70">
-        <v>-1.739335360000003</v>
+        <v>-1.945060880000006</v>
       </c>
       <c r="Q70">
-        <v>-19.23933536</v>
+        <v>-19.44506088000001</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.09296983422157462</v>
+        <v>0.0944914417771093</v>
       </c>
       <c r="T70">
-        <v>1.089372614816966</v>
+        <v>1.124513666907836</v>
       </c>
       <c r="U70">
         <v>0.1468</v>
       </c>
       <c r="V70">
-        <v>0.2627001144391751</v>
+        <v>0.2588928664038247</v>
       </c>
       <c r="W70">
-        <v>0.1082356232003291</v>
+        <v>0.1087945272119185</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7191,7 +7191,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.8756670481305837</v>
+        <v>0.8629762213460823</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7199,22 +7199,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1043605707271277</v>
+        <v>0.1053705707271277</v>
       </c>
       <c r="C71">
-        <v>-21.73421457562505</v>
+        <v>-24.79828340497247</v>
       </c>
       <c r="D71">
-        <v>113.863785424375</v>
+        <v>112.8017165950275</v>
       </c>
       <c r="E71">
-        <v>67.73800000000003</v>
+        <v>69.74000000000001</v>
       </c>
       <c r="F71">
-        <v>138.138</v>
+        <v>140.14</v>
       </c>
       <c r="G71">
         <v>2.54</v>
@@ -7235,37 +7235,37 @@
         <v>17.5</v>
       </c>
       <c r="M71">
-        <v>20.27865840000001</v>
+        <v>20.57255200000001</v>
       </c>
       <c r="N71">
-        <v>-2.778658400000008</v>
+        <v>-3.072552000000005</v>
       </c>
       <c r="O71">
-        <v>-0.8335975200000024</v>
+        <v>-0.9217656000000015</v>
       </c>
       <c r="P71">
-        <v>-1.945060880000006</v>
+        <v>-2.150786400000004</v>
       </c>
       <c r="Q71">
-        <v>-19.44506088000001</v>
+        <v>-19.6507864</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.0944914417771093</v>
+        <v>0.09611448983634627</v>
       </c>
       <c r="T71">
-        <v>1.124513666907836</v>
+        <v>1.161997455804763</v>
       </c>
       <c r="U71">
         <v>0.1468</v>
       </c>
       <c r="V71">
-        <v>0.2588928664038247</v>
+        <v>0.2551943968837701</v>
       </c>
       <c r="W71">
-        <v>0.1087945272119185</v>
+        <v>0.1093374625374626</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7273,7 +7273,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.8629762213460823</v>
+        <v>0.850647989612567</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7281,22 +7281,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1053705707271277</v>
+        <v>0.1063805707271277</v>
       </c>
       <c r="C72">
-        <v>-24.79828340497247</v>
+        <v>-27.84272235720314</v>
       </c>
       <c r="D72">
-        <v>112.8017165950275</v>
+        <v>111.7592776427969</v>
       </c>
       <c r="E72">
-        <v>69.74000000000001</v>
+        <v>71.74200000000002</v>
       </c>
       <c r="F72">
-        <v>140.14</v>
+        <v>142.142</v>
       </c>
       <c r="G72">
         <v>2.54</v>
@@ -7317,37 +7317,37 @@
         <v>17.5</v>
       </c>
       <c r="M72">
-        <v>20.57255200000001</v>
+        <v>20.86644560000001</v>
       </c>
       <c r="N72">
-        <v>-3.072552000000005</v>
+        <v>-3.366445600000006</v>
       </c>
       <c r="O72">
-        <v>-0.9217656000000015</v>
+        <v>-1.009933680000002</v>
       </c>
       <c r="P72">
-        <v>-2.150786400000004</v>
+        <v>-2.356511920000004</v>
       </c>
       <c r="Q72">
-        <v>-19.6507864</v>
+        <v>-19.85651192</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.09611448983634627</v>
+        <v>0.09784947224449614</v>
       </c>
       <c r="T72">
-        <v>1.161997455804763</v>
+        <v>1.202066333591135</v>
       </c>
       <c r="U72">
         <v>0.1468</v>
       </c>
       <c r="V72">
-        <v>0.2551943968837701</v>
+        <v>0.251600109603717</v>
       </c>
       <c r="W72">
-        <v>0.1093374625374626</v>
+        <v>0.1098651039101743</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7355,7 +7355,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.850647989612567</v>
+        <v>0.83866703201239</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7363,22 +7363,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1063805707271277</v>
+        <v>0.1073905707271277</v>
       </c>
       <c r="C73">
-        <v>-27.8427223572031</v>
+        <v>-30.8680706681285</v>
       </c>
       <c r="D73">
-        <v>111.7592776427969</v>
+        <v>110.7359293318715</v>
       </c>
       <c r="E73">
-        <v>71.74199999999999</v>
+        <v>73.744</v>
       </c>
       <c r="F73">
-        <v>142.142</v>
+        <v>144.144</v>
       </c>
       <c r="G73">
         <v>2.54</v>
@@ -7399,37 +7399,37 @@
         <v>17.5</v>
       </c>
       <c r="M73">
-        <v>20.8664456</v>
+        <v>21.1603392</v>
       </c>
       <c r="N73">
-        <v>-3.366445600000002</v>
+        <v>-3.660339200000003</v>
       </c>
       <c r="O73">
-        <v>-1.009933680000001</v>
+        <v>-1.098101760000001</v>
       </c>
       <c r="P73">
-        <v>-2.356511920000002</v>
+        <v>-2.562237440000002</v>
       </c>
       <c r="Q73">
-        <v>-19.85651192</v>
+        <v>-20.06223744</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.09784947224449611</v>
+        <v>0.09970838196751385</v>
       </c>
       <c r="T73">
-        <v>1.202066333591134</v>
+        <v>1.244997274076532</v>
       </c>
       <c r="U73">
         <v>0.1468</v>
       </c>
       <c r="V73">
-        <v>0.251600109603717</v>
+        <v>0.2481056636369987</v>
       </c>
       <c r="W73">
-        <v>0.1098651039101743</v>
+        <v>0.1103780885780886</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7437,7 +7437,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.8386670320123901</v>
+        <v>0.8270188787899959</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7445,22 +7445,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1073905707271277</v>
+        <v>0.1084005707271277</v>
       </c>
       <c r="C74">
-        <v>-30.8680706681285</v>
+        <v>-33.87484800224576</v>
       </c>
       <c r="D74">
-        <v>110.7359293318715</v>
+        <v>109.7311519977543</v>
       </c>
       <c r="E74">
-        <v>73.744</v>
+        <v>75.74600000000001</v>
       </c>
       <c r="F74">
-        <v>144.144</v>
+        <v>146.146</v>
       </c>
       <c r="G74">
         <v>2.54</v>
@@ -7481,37 +7481,37 @@
         <v>17.5</v>
       </c>
       <c r="M74">
-        <v>21.1603392</v>
+        <v>21.4542328</v>
       </c>
       <c r="N74">
-        <v>-3.660339200000003</v>
+        <v>-3.954232800000003</v>
       </c>
       <c r="O74">
-        <v>-1.098101760000001</v>
+        <v>-1.186269840000001</v>
       </c>
       <c r="P74">
-        <v>-2.562237440000002</v>
+        <v>-2.767962960000002</v>
       </c>
       <c r="Q74">
-        <v>-20.06223744</v>
+        <v>-20.26796296</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.09970838196751385</v>
+        <v>0.1017049887070514</v>
       </c>
       <c r="T74">
-        <v>1.244997274076532</v>
+        <v>1.291108284227515</v>
       </c>
       <c r="U74">
         <v>0.1468</v>
       </c>
       <c r="V74">
-        <v>0.2481056636369987</v>
+        <v>0.244706955915944</v>
       </c>
       <c r="W74">
-        <v>0.1103780885780886</v>
+        <v>0.1108770188715394</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7519,7 +7519,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.8270188787899959</v>
+        <v>0.8156898530531466</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7527,22 +7527,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1084005707271277</v>
+        <v>0.1094105707271277</v>
       </c>
       <c r="C75">
-        <v>-33.87484800224576</v>
+        <v>-36.86355533266821</v>
       </c>
       <c r="D75">
-        <v>109.7311519977543</v>
+        <v>108.7444446673318</v>
       </c>
       <c r="E75">
-        <v>75.74600000000001</v>
+        <v>77.74800000000002</v>
       </c>
       <c r="F75">
-        <v>146.146</v>
+        <v>148.148</v>
       </c>
       <c r="G75">
         <v>2.54</v>
@@ -7563,37 +7563,37 @@
         <v>17.5</v>
       </c>
       <c r="M75">
-        <v>21.4542328</v>
+        <v>21.74812640000001</v>
       </c>
       <c r="N75">
-        <v>-3.954232800000003</v>
+        <v>-4.248126400000007</v>
       </c>
       <c r="O75">
-        <v>-1.186269840000001</v>
+        <v>-1.274437920000002</v>
       </c>
       <c r="P75">
-        <v>-2.767962960000002</v>
+        <v>-2.973688480000005</v>
       </c>
       <c r="Q75">
-        <v>-20.26796296</v>
+        <v>-20.47368848000001</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1017049887070514</v>
+        <v>0.1038551805803995</v>
       </c>
       <c r="T75">
-        <v>1.291108284227515</v>
+        <v>1.340766295159342</v>
       </c>
       <c r="U75">
         <v>0.1468</v>
       </c>
       <c r="V75">
-        <v>0.244706955915944</v>
+        <v>0.2414001051603231</v>
       </c>
       <c r="W75">
-        <v>0.1108770188715394</v>
+        <v>0.1113624645624646</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7601,7 +7601,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.8156898530531466</v>
+        <v>0.8046670172010768</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7609,22 +7609,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1094105707271277</v>
+        <v>0.1518034024522264</v>
       </c>
       <c r="C76">
-        <v>-36.86355533266821</v>
+        <v>-68.66230658458784</v>
       </c>
       <c r="D76">
-        <v>108.7444446673318</v>
+        <v>78.94769341541216</v>
       </c>
       <c r="E76">
-        <v>77.74800000000002</v>
+        <v>79.75</v>
       </c>
       <c r="F76">
-        <v>148.148</v>
+        <v>150.15</v>
       </c>
       <c r="G76">
         <v>2.54</v>
@@ -7645,45 +7645,45 @@
         <v>17.5</v>
       </c>
       <c r="M76">
-        <v>21.74812640000001</v>
+        <v>30.15012</v>
       </c>
       <c r="N76">
-        <v>-4.248126400000007</v>
+        <v>-12.65012</v>
       </c>
       <c r="O76">
-        <v>-1.274437920000002</v>
+        <v>-3.795036</v>
       </c>
       <c r="P76">
-        <v>-2.973688480000005</v>
+        <v>-8.855084000000002</v>
       </c>
       <c r="Q76">
-        <v>-20.47368848000001</v>
+        <v>-26.355084</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1038551805803995</v>
+        <v>0.1097087147040105</v>
       </c>
       <c r="T76">
-        <v>1.340766295159342</v>
+        <v>1.475951840739273</v>
       </c>
       <c r="U76">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V76">
-        <v>0.2414001051603231</v>
+        <v>0.1741286601844371</v>
       </c>
       <c r="W76">
-        <v>0.1113624645624646</v>
+        <v>0.165834965034965</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y76">
-        <v>0.8046670172010768</v>
+        <v>0.5804288672814569</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7691,22 +7691,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1518034024522264</v>
+        <v>0.1533534024522264</v>
       </c>
       <c r="C77">
-        <v>-68.66230658458784</v>
+        <v>-71.44739579415008</v>
       </c>
       <c r="D77">
-        <v>78.94769341541216</v>
+        <v>78.16460420584993</v>
       </c>
       <c r="E77">
-        <v>79.75</v>
+        <v>81.75200000000001</v>
       </c>
       <c r="F77">
-        <v>150.15</v>
+        <v>152.152</v>
       </c>
       <c r="G77">
         <v>2.54</v>
@@ -7727,37 +7727,37 @@
         <v>17.5</v>
       </c>
       <c r="M77">
-        <v>30.15012</v>
+        <v>30.5521216</v>
       </c>
       <c r="N77">
-        <v>-12.65012</v>
+        <v>-13.0521216</v>
       </c>
       <c r="O77">
-        <v>-3.795036</v>
+        <v>-3.915636480000001</v>
       </c>
       <c r="P77">
-        <v>-8.855084000000002</v>
+        <v>-9.136485120000003</v>
       </c>
       <c r="Q77">
-        <v>-26.355084</v>
+        <v>-26.63648512</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1097087147040105</v>
+        <v>0.1123715778166776</v>
       </c>
       <c r="T77">
-        <v>1.475951840739273</v>
+        <v>1.53744983410341</v>
       </c>
       <c r="U77">
         <v>0.2008</v>
       </c>
       <c r="V77">
-        <v>0.1741286601844371</v>
+        <v>0.1718374936030629</v>
       </c>
       <c r="W77">
-        <v>0.165834965034965</v>
+        <v>0.166295031284505</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7765,7 +7765,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.5804288672814569</v>
+        <v>0.5727916453435429</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7773,22 +7773,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1533534024522264</v>
+        <v>0.1549034024522264</v>
       </c>
       <c r="C78">
-        <v>-71.44739579415008</v>
+        <v>-74.21710252056234</v>
       </c>
       <c r="D78">
-        <v>78.16460420584993</v>
+        <v>77.39689747943768</v>
       </c>
       <c r="E78">
-        <v>81.75200000000001</v>
+        <v>83.75400000000002</v>
       </c>
       <c r="F78">
-        <v>152.152</v>
+        <v>154.154</v>
       </c>
       <c r="G78">
         <v>2.54</v>
@@ -7809,37 +7809,37 @@
         <v>17.5</v>
       </c>
       <c r="M78">
-        <v>30.5521216</v>
+        <v>30.95412320000001</v>
       </c>
       <c r="N78">
-        <v>-13.0521216</v>
+        <v>-13.45412320000001</v>
       </c>
       <c r="O78">
-        <v>-3.915636480000001</v>
+        <v>-4.036236960000001</v>
       </c>
       <c r="P78">
-        <v>-9.136485120000003</v>
+        <v>-9.417886240000005</v>
       </c>
       <c r="Q78">
-        <v>-26.63648512</v>
+        <v>-26.91788624</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1123715778166776</v>
+        <v>0.1152659942434897</v>
       </c>
       <c r="T78">
-        <v>1.53744983410341</v>
+        <v>1.604295479064427</v>
       </c>
       <c r="U78">
         <v>0.2008</v>
       </c>
       <c r="V78">
-        <v>0.1718374936030629</v>
+        <v>0.1696058378419841</v>
       </c>
       <c r="W78">
-        <v>0.166295031284505</v>
+        <v>0.1667431477613296</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7847,7 +7847,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.5727916453435429</v>
+        <v>0.5653527928066138</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7855,22 +7855,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1549034024522264</v>
+        <v>0.1564534024522264</v>
       </c>
       <c r="C79">
-        <v>-74.21710252056234</v>
+        <v>-76.97187560039009</v>
       </c>
       <c r="D79">
-        <v>77.39689747943768</v>
+        <v>76.64412439960991</v>
       </c>
       <c r="E79">
-        <v>83.75400000000002</v>
+        <v>85.756</v>
       </c>
       <c r="F79">
-        <v>154.154</v>
+        <v>156.156</v>
       </c>
       <c r="G79">
         <v>2.54</v>
@@ -7891,37 +7891,37 @@
         <v>17.5</v>
       </c>
       <c r="M79">
-        <v>30.95412320000001</v>
+        <v>31.3561248</v>
       </c>
       <c r="N79">
-        <v>-13.45412320000001</v>
+        <v>-13.8561248</v>
       </c>
       <c r="O79">
-        <v>-4.036236960000001</v>
+        <v>-4.156837440000001</v>
       </c>
       <c r="P79">
-        <v>-9.417886240000005</v>
+        <v>-9.699287360000003</v>
       </c>
       <c r="Q79">
-        <v>-26.91788624</v>
+        <v>-27.19928736</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.1152659942434897</v>
+        <v>0.1184235394363756</v>
       </c>
       <c r="T79">
-        <v>1.604295479064427</v>
+        <v>1.677218000840083</v>
       </c>
       <c r="U79">
         <v>0.2008</v>
       </c>
       <c r="V79">
-        <v>0.1696058378419841</v>
+        <v>0.1674314040234972</v>
       </c>
       <c r="W79">
-        <v>0.1667431477613296</v>
+        <v>0.1671797740720818</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7929,7 +7929,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.5653527928066138</v>
+        <v>0.5581046800783239</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7937,22 +7937,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1564534024522264</v>
+        <v>0.1580034024522264</v>
       </c>
       <c r="C80">
-        <v>-76.97187560039009</v>
+        <v>-79.71214657660931</v>
       </c>
       <c r="D80">
-        <v>76.64412439960991</v>
+        <v>75.9058534233907</v>
       </c>
       <c r="E80">
-        <v>85.756</v>
+        <v>87.75800000000001</v>
       </c>
       <c r="F80">
-        <v>156.156</v>
+        <v>158.158</v>
       </c>
       <c r="G80">
         <v>2.54</v>
@@ -7973,37 +7973,37 @@
         <v>17.5</v>
       </c>
       <c r="M80">
-        <v>31.3561248</v>
+        <v>31.75812640000001</v>
       </c>
       <c r="N80">
-        <v>-13.8561248</v>
+        <v>-14.25812640000001</v>
       </c>
       <c r="O80">
-        <v>-4.156837440000001</v>
+        <v>-4.277437920000001</v>
       </c>
       <c r="P80">
-        <v>-9.699287360000003</v>
+        <v>-9.980688480000005</v>
       </c>
       <c r="Q80">
-        <v>-27.19928736</v>
+        <v>-27.48068848</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.1184235394363756</v>
+        <v>0.1218818032190602</v>
       </c>
       <c r="T80">
-        <v>1.677218000840083</v>
+        <v>1.757085524689611</v>
       </c>
       <c r="U80">
         <v>0.2008</v>
       </c>
       <c r="V80">
-        <v>0.1674314040234972</v>
+        <v>0.1653120191624402</v>
       </c>
       <c r="W80">
-        <v>0.1671797740720818</v>
+        <v>0.167605346552182</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -8011,7 +8011,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.5581046800783239</v>
+        <v>0.5510400638748008</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -8019,22 +8019,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1580034024522264</v>
+        <v>0.1595534024522264</v>
       </c>
       <c r="C81">
-        <v>-79.71214657660931</v>
+        <v>-82.43833052355832</v>
       </c>
       <c r="D81">
-        <v>75.9058534233907</v>
+        <v>75.1816694764417</v>
       </c>
       <c r="E81">
-        <v>87.75800000000001</v>
+        <v>89.76000000000002</v>
       </c>
       <c r="F81">
-        <v>158.158</v>
+        <v>160.16</v>
       </c>
       <c r="G81">
         <v>2.54</v>
@@ -8055,37 +8055,37 @@
         <v>17.5</v>
       </c>
       <c r="M81">
-        <v>31.75812640000001</v>
+        <v>32.16012800000001</v>
       </c>
       <c r="N81">
-        <v>-14.25812640000001</v>
+        <v>-14.66012800000001</v>
       </c>
       <c r="O81">
-        <v>-4.277437920000001</v>
+        <v>-4.398038400000002</v>
       </c>
       <c r="P81">
-        <v>-9.980688480000005</v>
+        <v>-10.26208960000001</v>
       </c>
       <c r="Q81">
-        <v>-27.48068848</v>
+        <v>-27.76208960000001</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.1218818032190602</v>
+        <v>0.1256858933800132</v>
       </c>
       <c r="T81">
-        <v>1.757085524689611</v>
+        <v>1.844939800924092</v>
       </c>
       <c r="U81">
         <v>0.2008</v>
       </c>
       <c r="V81">
-        <v>0.1653120191624402</v>
+        <v>0.1632456189229097</v>
       </c>
       <c r="W81">
-        <v>0.167605346552182</v>
+        <v>0.1680202797202797</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -8093,7 +8093,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.5510400638748008</v>
+        <v>0.5441520630763658</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -8101,22 +8101,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1595534024522264</v>
+        <v>0.1611034024522264</v>
       </c>
       <c r="C82">
-        <v>-82.43833052355832</v>
+        <v>-85.15082682511354</v>
       </c>
       <c r="D82">
-        <v>75.1816694764417</v>
+        <v>74.47117317488649</v>
       </c>
       <c r="E82">
-        <v>89.76000000000002</v>
+        <v>91.76200000000003</v>
       </c>
       <c r="F82">
-        <v>160.16</v>
+        <v>162.162</v>
       </c>
       <c r="G82">
         <v>2.54</v>
@@ -8137,37 +8137,37 @@
         <v>17.5</v>
       </c>
       <c r="M82">
-        <v>32.16012800000001</v>
+        <v>32.56212960000001</v>
       </c>
       <c r="N82">
-        <v>-14.66012800000001</v>
+        <v>-15.06212960000001</v>
       </c>
       <c r="O82">
-        <v>-4.398038400000002</v>
+        <v>-4.518638880000002</v>
       </c>
       <c r="P82">
-        <v>-10.26208960000001</v>
+        <v>-10.54349072</v>
       </c>
       <c r="Q82">
-        <v>-27.76208960000001</v>
+        <v>-28.04349072</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.1256858933800132</v>
+        <v>0.1298904140842244</v>
       </c>
       <c r="T82">
-        <v>1.844939800924092</v>
+        <v>1.94204189570957</v>
       </c>
       <c r="U82">
         <v>0.2008</v>
       </c>
       <c r="V82">
-        <v>0.1632456189229097</v>
+        <v>0.1612302409115158</v>
       </c>
       <c r="W82">
-        <v>0.1680202797202797</v>
+        <v>0.1684249676249676</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8175,7 +8175,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.5441520630763658</v>
+        <v>0.5374341363717192</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8183,22 +8183,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1611034024522264</v>
+        <v>0.1626534024522264</v>
       </c>
       <c r="C83">
-        <v>-85.15082682511354</v>
+        <v>-87.85001990915356</v>
       </c>
       <c r="D83">
-        <v>74.47117317488649</v>
+        <v>73.77398009084645</v>
       </c>
       <c r="E83">
-        <v>91.76200000000003</v>
+        <v>93.76400000000001</v>
       </c>
       <c r="F83">
-        <v>162.162</v>
+        <v>164.164</v>
       </c>
       <c r="G83">
         <v>2.54</v>
@@ -8219,37 +8219,37 @@
         <v>17.5</v>
       </c>
       <c r="M83">
-        <v>32.56212960000001</v>
+        <v>32.9641312</v>
       </c>
       <c r="N83">
-        <v>-15.06212960000001</v>
+        <v>-15.4641312</v>
       </c>
       <c r="O83">
-        <v>-4.518638880000002</v>
+        <v>-4.639239360000001</v>
       </c>
       <c r="P83">
-        <v>-10.54349072</v>
+        <v>-10.82489184</v>
       </c>
       <c r="Q83">
-        <v>-28.04349072</v>
+        <v>-28.32489184</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.1298904140842244</v>
+        <v>0.1345621037555702</v>
       </c>
       <c r="T83">
-        <v>1.94204189570957</v>
+        <v>2.04993311213788</v>
       </c>
       <c r="U83">
         <v>0.2008</v>
       </c>
       <c r="V83">
-        <v>0.1612302409115158</v>
+        <v>0.1592640184613754</v>
       </c>
       <c r="W83">
-        <v>0.1684249676249676</v>
+        <v>0.1688197850929558</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8257,7 +8257,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.5374341363717192</v>
+        <v>0.5308800615379179</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8265,22 +8265,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1626534024522264</v>
+        <v>0.1642034024522264</v>
       </c>
       <c r="C84">
-        <v>-87.85001990915356</v>
+        <v>-90.53627994114989</v>
       </c>
       <c r="D84">
-        <v>73.77398009084645</v>
+        <v>73.08972005885013</v>
       </c>
       <c r="E84">
-        <v>93.76400000000001</v>
+        <v>95.76600000000002</v>
       </c>
       <c r="F84">
-        <v>164.164</v>
+        <v>166.166</v>
       </c>
       <c r="G84">
         <v>2.54</v>
@@ -8301,37 +8301,37 @@
         <v>17.5</v>
       </c>
       <c r="M84">
-        <v>32.9641312</v>
+        <v>33.3661328</v>
       </c>
       <c r="N84">
-        <v>-15.4641312</v>
+        <v>-15.8661328</v>
       </c>
       <c r="O84">
-        <v>-4.639239360000001</v>
+        <v>-4.759839840000001</v>
       </c>
       <c r="P84">
-        <v>-10.82489184</v>
+        <v>-11.10629296</v>
       </c>
       <c r="Q84">
-        <v>-28.32489184</v>
+        <v>-28.60629296</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.1345621037555702</v>
+        <v>0.1397834039764861</v>
       </c>
       <c r="T84">
-        <v>2.04993311213788</v>
+        <v>2.170517412851873</v>
       </c>
       <c r="U84">
         <v>0.2008</v>
       </c>
       <c r="V84">
-        <v>0.1592640184613754</v>
+        <v>0.1573451748654552</v>
       </c>
       <c r="W84">
-        <v>0.1688197850929558</v>
+        <v>0.1692050888870166</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8339,7 +8339,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.5308800615379179</v>
+        <v>0.5244839162181839</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8347,22 +8347,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1642034024522264</v>
+        <v>0.1657534024522264</v>
       </c>
       <c r="C85">
-        <v>-90.53627994114989</v>
+        <v>-93.20996347951392</v>
       </c>
       <c r="D85">
-        <v>73.08972005885013</v>
+        <v>72.41803652048611</v>
       </c>
       <c r="E85">
-        <v>95.76600000000002</v>
+        <v>97.76800000000003</v>
       </c>
       <c r="F85">
-        <v>166.166</v>
+        <v>168.168</v>
       </c>
       <c r="G85">
         <v>2.54</v>
@@ -8383,37 +8383,37 @@
         <v>17.5</v>
       </c>
       <c r="M85">
-        <v>33.3661328</v>
+        <v>33.76813440000001</v>
       </c>
       <c r="N85">
-        <v>-15.8661328</v>
+        <v>-16.26813440000001</v>
       </c>
       <c r="O85">
-        <v>-4.759839840000001</v>
+        <v>-4.880440320000003</v>
       </c>
       <c r="P85">
-        <v>-11.10629296</v>
+        <v>-11.38769408000001</v>
       </c>
       <c r="Q85">
-        <v>-28.60629296</v>
+        <v>-28.88769408000001</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.1397834039764861</v>
+        <v>0.1456573667250165</v>
       </c>
       <c r="T85">
-        <v>2.170517412851873</v>
+        <v>2.306174751155116</v>
       </c>
       <c r="U85">
         <v>0.2008</v>
       </c>
       <c r="V85">
-        <v>0.1573451748654552</v>
+        <v>0.1554720180218188</v>
       </c>
       <c r="W85">
-        <v>0.1692050888870166</v>
+        <v>0.1695812187812188</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8421,7 +8421,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.5244839162181839</v>
+        <v>0.5182400600727293</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8429,22 +8429,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.1657534024522264</v>
+        <v>0.1673034024522264</v>
       </c>
       <c r="C86">
-        <v>-93.20996347951387</v>
+        <v>-95.87141409513767</v>
       </c>
       <c r="D86">
-        <v>72.41803652048613</v>
+        <v>71.75858590486234</v>
       </c>
       <c r="E86">
-        <v>97.768</v>
+        <v>99.77000000000001</v>
       </c>
       <c r="F86">
-        <v>168.168</v>
+        <v>170.17</v>
       </c>
       <c r="G86">
         <v>2.54</v>
@@ -8465,37 +8465,37 @@
         <v>17.5</v>
       </c>
       <c r="M86">
-        <v>33.7681344</v>
+        <v>34.17013600000001</v>
       </c>
       <c r="N86">
-        <v>-16.2681344</v>
+        <v>-16.67013600000001</v>
       </c>
       <c r="O86">
-        <v>-4.88044032</v>
+        <v>-5.001040800000002</v>
       </c>
       <c r="P86">
-        <v>-11.38769408</v>
+        <v>-11.6690952</v>
       </c>
       <c r="Q86">
-        <v>-28.88769408</v>
+        <v>-29.1690952</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.1456573667250164</v>
+        <v>0.1523145245066842</v>
       </c>
       <c r="T86">
-        <v>2.306174751155114</v>
+        <v>2.459919734565455</v>
       </c>
       <c r="U86">
         <v>0.2008</v>
       </c>
       <c r="V86">
-        <v>0.1554720180218188</v>
+        <v>0.1536429354568562</v>
       </c>
       <c r="W86">
-        <v>0.1695812187812188</v>
+        <v>0.1699484985602633</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8503,7 +8503,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.5182400600727294</v>
+        <v>0.5121431181895207</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8511,22 +8511,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1673034024522264</v>
+        <v>0.1688534024522264</v>
       </c>
       <c r="C87">
-        <v>-95.87141409513767</v>
+        <v>-98.52096295739005</v>
       </c>
       <c r="D87">
-        <v>71.75858590486234</v>
+        <v>71.11103704260996</v>
       </c>
       <c r="E87">
-        <v>99.77000000000001</v>
+        <v>101.772</v>
       </c>
       <c r="F87">
-        <v>170.17</v>
+        <v>172.172</v>
       </c>
       <c r="G87">
         <v>2.54</v>
@@ -8547,37 +8547,37 @@
         <v>17.5</v>
       </c>
       <c r="M87">
-        <v>34.17013600000001</v>
+        <v>34.5721376</v>
       </c>
       <c r="N87">
-        <v>-16.67013600000001</v>
+        <v>-17.0721376</v>
       </c>
       <c r="O87">
-        <v>-5.001040800000002</v>
+        <v>-5.121641280000001</v>
       </c>
       <c r="P87">
-        <v>-11.6690952</v>
+        <v>-11.95049632</v>
       </c>
       <c r="Q87">
-        <v>-29.1690952</v>
+        <v>-29.45049632</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.1523145245066842</v>
+        <v>0.1599227048285902</v>
       </c>
       <c r="T87">
-        <v>2.459919734565455</v>
+        <v>2.635628287034416</v>
       </c>
       <c r="U87">
         <v>0.2008</v>
       </c>
       <c r="V87">
-        <v>0.1536429354568562</v>
+        <v>0.15185638969573</v>
       </c>
       <c r="W87">
-        <v>0.1699484985602633</v>
+        <v>0.1703072369490974</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8585,7 +8585,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.5121431181895207</v>
+        <v>0.5061879656524333</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8593,22 +8593,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.1688534024522264</v>
+        <v>0.1704034024522264</v>
       </c>
       <c r="C88">
-        <v>-98.52096295739005</v>
+        <v>-101.1589293886688</v>
       </c>
       <c r="D88">
-        <v>71.11103704260996</v>
+        <v>70.4750706113312</v>
       </c>
       <c r="E88">
-        <v>101.772</v>
+        <v>103.774</v>
       </c>
       <c r="F88">
-        <v>172.172</v>
+        <v>174.174</v>
       </c>
       <c r="G88">
         <v>2.54</v>
@@ -8629,37 +8629,37 @@
         <v>17.5</v>
       </c>
       <c r="M88">
-        <v>34.5721376</v>
+        <v>34.9741392</v>
       </c>
       <c r="N88">
-        <v>-17.0721376</v>
+        <v>-17.4741392</v>
       </c>
       <c r="O88">
-        <v>-5.121641280000001</v>
+        <v>-5.242241760000001</v>
       </c>
       <c r="P88">
-        <v>-11.95049632</v>
+        <v>-12.23189744</v>
       </c>
       <c r="Q88">
-        <v>-29.45049632</v>
+        <v>-29.73189744</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.1599227048285902</v>
+        <v>0.1687013744307895</v>
       </c>
       <c r="T88">
-        <v>2.635628287034416</v>
+        <v>2.838368924498602</v>
       </c>
       <c r="U88">
         <v>0.2008</v>
       </c>
       <c r="V88">
-        <v>0.15185638969573</v>
+        <v>0.1501109139521009</v>
       </c>
       <c r="W88">
-        <v>0.1703072369490974</v>
+        <v>0.1706577284784181</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8667,7 +8667,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.5061879656524333</v>
+        <v>0.5003697131736697</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8675,22 +8675,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.1704034024522264</v>
+        <v>0.2031096357167285</v>
       </c>
       <c r="C89">
-        <v>-101.1589293886688</v>
+        <v>-114.3490062501527</v>
       </c>
       <c r="D89">
-        <v>70.4750706113312</v>
+        <v>59.28699374984735</v>
       </c>
       <c r="E89">
-        <v>103.774</v>
+        <v>105.776</v>
       </c>
       <c r="F89">
-        <v>174.174</v>
+        <v>176.176</v>
       </c>
       <c r="G89">
         <v>2.54</v>
@@ -8711,45 +8711,45 @@
         <v>17.5</v>
       </c>
       <c r="M89">
-        <v>34.9741392</v>
+        <v>41.54230080000001</v>
       </c>
       <c r="N89">
-        <v>-17.4741392</v>
+        <v>-24.04230080000001</v>
       </c>
       <c r="O89">
-        <v>-5.242241760000001</v>
+        <v>-7.212690240000001</v>
       </c>
       <c r="P89">
-        <v>-12.23189744</v>
+        <v>-16.82961056000001</v>
       </c>
       <c r="Q89">
-        <v>-29.73189744</v>
+        <v>-34.32961056000001</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.1687013744307895</v>
+        <v>0.1819117661708723</v>
       </c>
       <c r="T89">
-        <v>2.838368924498602</v>
+        <v>3.143458803022455</v>
       </c>
       <c r="U89">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.1501109139521009</v>
+        <v>0.1263772082647863</v>
       </c>
       <c r="W89">
-        <v>0.1706577284784181</v>
+        <v>0.2060002542911634</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y89">
-        <v>0.5003697131736697</v>
+        <v>0.421257360882621</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8757,22 +8757,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2031096357167285</v>
+        <v>0.2050096357167284</v>
       </c>
       <c r="C90">
-        <v>-114.3490062501527</v>
+        <v>-116.8927769946113</v>
       </c>
       <c r="D90">
-        <v>59.28699374984735</v>
+        <v>58.74522300538874</v>
       </c>
       <c r="E90">
-        <v>105.776</v>
+        <v>107.778</v>
       </c>
       <c r="F90">
-        <v>176.176</v>
+        <v>178.178</v>
       </c>
       <c r="G90">
         <v>2.54</v>
@@ -8793,37 +8793,37 @@
         <v>17.5</v>
       </c>
       <c r="M90">
-        <v>41.54230080000001</v>
+        <v>42.01437240000001</v>
       </c>
       <c r="N90">
-        <v>-24.04230080000001</v>
+        <v>-24.51437240000001</v>
       </c>
       <c r="O90">
-        <v>-7.212690240000001</v>
+        <v>-7.354311720000002</v>
       </c>
       <c r="P90">
-        <v>-16.82961056000001</v>
+        <v>-17.16006068</v>
       </c>
       <c r="Q90">
-        <v>-34.32961056000001</v>
+        <v>-34.66006068</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.1819117661708723</v>
+        <v>0.1942855630954971</v>
       </c>
       <c r="T90">
-        <v>3.143458803022455</v>
+        <v>3.429227785115406</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.1263772082647863</v>
+        <v>0.1249572396325977</v>
       </c>
       <c r="W90">
-        <v>0.2060002542911634</v>
+        <v>0.2063350828946335</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8831,7 +8831,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.421257360882621</v>
+        <v>0.416524132108659</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8839,22 +8839,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2050096357167284</v>
+        <v>0.2069096357167285</v>
       </c>
       <c r="C91">
-        <v>-116.8927769946113</v>
+        <v>-119.4267358854563</v>
       </c>
       <c r="D91">
-        <v>58.74522300538874</v>
+        <v>58.21326411454375</v>
       </c>
       <c r="E91">
-        <v>107.778</v>
+        <v>109.78</v>
       </c>
       <c r="F91">
-        <v>178.178</v>
+        <v>180.18</v>
       </c>
       <c r="G91">
         <v>2.54</v>
@@ -8875,37 +8875,37 @@
         <v>17.5</v>
       </c>
       <c r="M91">
-        <v>42.01437240000001</v>
+        <v>42.48644400000001</v>
       </c>
       <c r="N91">
-        <v>-24.51437240000001</v>
+        <v>-24.98644400000001</v>
       </c>
       <c r="O91">
-        <v>-7.354311720000002</v>
+        <v>-7.495933200000001</v>
       </c>
       <c r="P91">
-        <v>-17.16006068</v>
+        <v>-17.4905108</v>
       </c>
       <c r="Q91">
-        <v>-34.66006068</v>
+        <v>-34.9905108</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.1942855630954971</v>
+        <v>0.2091341194050468</v>
       </c>
       <c r="T91">
-        <v>3.429227785115406</v>
+        <v>3.772150563626946</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.1249572396325977</v>
+        <v>0.1235688258589022</v>
       </c>
       <c r="W91">
-        <v>0.2063350828946335</v>
+        <v>0.2066624708624709</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8913,7 +8913,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.416524132108659</v>
+        <v>0.4118960861963405</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8921,22 +8921,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2069096357167285</v>
+        <v>0.2088096357167284</v>
       </c>
       <c r="C92">
-        <v>-119.4267358854563</v>
+        <v>-121.9511470801221</v>
       </c>
       <c r="D92">
-        <v>58.21326411454375</v>
+        <v>57.69085291987789</v>
       </c>
       <c r="E92">
-        <v>109.78</v>
+        <v>111.782</v>
       </c>
       <c r="F92">
-        <v>180.18</v>
+        <v>182.182</v>
       </c>
       <c r="G92">
         <v>2.54</v>
@@ -8957,37 +8957,37 @@
         <v>17.5</v>
       </c>
       <c r="M92">
-        <v>42.48644400000001</v>
+        <v>42.95851560000001</v>
       </c>
       <c r="N92">
-        <v>-24.98644400000001</v>
+        <v>-25.45851560000001</v>
       </c>
       <c r="O92">
-        <v>-7.495933200000001</v>
+        <v>-7.637554680000001</v>
       </c>
       <c r="P92">
-        <v>-17.4905108</v>
+        <v>-17.82096092</v>
       </c>
       <c r="Q92">
-        <v>-34.9905108</v>
+        <v>-35.32096092</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.2091341194050468</v>
+        <v>0.2272823548944965</v>
       </c>
       <c r="T92">
-        <v>3.772150563626946</v>
+        <v>4.191278404029941</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.1235688258589022</v>
+        <v>0.1222109266736395</v>
       </c>
       <c r="W92">
-        <v>0.2066624708624709</v>
+        <v>0.2069826634903558</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8995,7 +8995,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.4118960861963405</v>
+        <v>0.4073697555787984</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -9003,22 +9003,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2088096357167284</v>
+        <v>0.2107096357167285</v>
       </c>
       <c r="C93">
-        <v>-121.9511470801221</v>
+        <v>-124.466265338089</v>
       </c>
       <c r="D93">
-        <v>57.69085291987789</v>
+        <v>57.17773466191105</v>
       </c>
       <c r="E93">
-        <v>111.782</v>
+        <v>113.784</v>
       </c>
       <c r="F93">
-        <v>182.182</v>
+        <v>184.184</v>
       </c>
       <c r="G93">
         <v>2.54</v>
@@ -9039,37 +9039,37 @@
         <v>17.5</v>
       </c>
       <c r="M93">
-        <v>42.95851560000001</v>
+        <v>43.43058720000001</v>
       </c>
       <c r="N93">
-        <v>-25.45851560000001</v>
+        <v>-25.93058720000001</v>
       </c>
       <c r="O93">
-        <v>-7.637554680000001</v>
+        <v>-7.779176160000001</v>
       </c>
       <c r="P93">
-        <v>-17.82096092</v>
+        <v>-18.15141104</v>
       </c>
       <c r="Q93">
-        <v>-35.32096092</v>
+        <v>-35.65141104</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.2272823548944965</v>
+        <v>0.2499676492563086</v>
       </c>
       <c r="T93">
-        <v>4.191278404029941</v>
+        <v>4.715188204533685</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.1222109266736395</v>
+        <v>0.1208825470358826</v>
       </c>
       <c r="W93">
-        <v>0.2069826634903558</v>
+        <v>0.2072958954089389</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -9077,7 +9077,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.4073697555787984</v>
+        <v>0.4029418234529419</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -9085,22 +9085,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2107096357167285</v>
+        <v>0.2126096357167285</v>
       </c>
       <c r="C94">
-        <v>-124.466265338089</v>
+        <v>-126.9723364351377</v>
       </c>
       <c r="D94">
-        <v>57.17773466191105</v>
+        <v>56.6736635648623</v>
       </c>
       <c r="E94">
-        <v>113.784</v>
+        <v>115.786</v>
       </c>
       <c r="F94">
-        <v>184.184</v>
+        <v>186.186</v>
       </c>
       <c r="G94">
         <v>2.54</v>
@@ -9121,37 +9121,37 @@
         <v>17.5</v>
       </c>
       <c r="M94">
-        <v>43.43058720000001</v>
+        <v>43.90265880000001</v>
       </c>
       <c r="N94">
-        <v>-25.93058720000001</v>
+        <v>-26.40265880000001</v>
       </c>
       <c r="O94">
-        <v>-7.779176160000001</v>
+        <v>-7.920797640000004</v>
       </c>
       <c r="P94">
-        <v>-18.15141104</v>
+        <v>-18.48186116000001</v>
       </c>
       <c r="Q94">
-        <v>-35.65141104</v>
+        <v>-35.98186116000001</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.2499676492563086</v>
+        <v>0.2791344562929241</v>
       </c>
       <c r="T94">
-        <v>4.715188204533685</v>
+        <v>5.388786519467069</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.1208825470358826</v>
+        <v>0.1195827347021634</v>
       </c>
       <c r="W94">
-        <v>0.2072958954089389</v>
+        <v>0.2076023911572299</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9159,7 +9159,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.4029418234529419</v>
+        <v>0.3986091156738779</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9167,22 +9167,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2126096357167285</v>
+        <v>0.2145096357167285</v>
       </c>
       <c r="C95">
-        <v>-126.9723364351377</v>
+        <v>-129.469597555885</v>
       </c>
       <c r="D95">
-        <v>56.6736635648623</v>
+        <v>56.17840244411498</v>
       </c>
       <c r="E95">
-        <v>115.786</v>
+        <v>117.788</v>
       </c>
       <c r="F95">
-        <v>186.186</v>
+        <v>188.188</v>
       </c>
       <c r="G95">
         <v>2.54</v>
@@ -9203,37 +9203,37 @@
         <v>17.5</v>
       </c>
       <c r="M95">
-        <v>43.90265880000001</v>
+        <v>44.3747304</v>
       </c>
       <c r="N95">
-        <v>-26.40265880000001</v>
+        <v>-26.8747304</v>
       </c>
       <c r="O95">
-        <v>-7.920797640000004</v>
+        <v>-8.062419120000001</v>
       </c>
       <c r="P95">
-        <v>-18.48186116000001</v>
+        <v>-18.81231128</v>
       </c>
       <c r="Q95">
-        <v>-35.98186116000001</v>
+        <v>-36.31231128</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.2791344562929241</v>
+        <v>0.3180235323417449</v>
       </c>
       <c r="T95">
-        <v>5.388786519467069</v>
+        <v>6.286917606044915</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.1195827347021634</v>
+        <v>0.1183105779500127</v>
       </c>
       <c r="W95">
-        <v>0.2076023911572299</v>
+        <v>0.207902365719387</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9241,7 +9241,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.3986091156738779</v>
+        <v>0.3943685931667091</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9249,22 +9249,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2145096357167285</v>
+        <v>0.2164096357167285</v>
       </c>
       <c r="C96">
-        <v>-129.469597555885</v>
+        <v>-131.9582776659146</v>
       </c>
       <c r="D96">
-        <v>56.17840244411498</v>
+        <v>55.69172233408538</v>
       </c>
       <c r="E96">
-        <v>117.788</v>
+        <v>119.79</v>
       </c>
       <c r="F96">
-        <v>188.188</v>
+        <v>190.19</v>
       </c>
       <c r="G96">
         <v>2.54</v>
@@ -9285,37 +9285,37 @@
         <v>17.5</v>
       </c>
       <c r="M96">
-        <v>44.3747304</v>
+        <v>44.84680200000001</v>
       </c>
       <c r="N96">
-        <v>-26.8747304</v>
+        <v>-27.34680200000001</v>
       </c>
       <c r="O96">
-        <v>-8.062419120000001</v>
+        <v>-8.204040600000003</v>
       </c>
       <c r="P96">
-        <v>-18.81231128</v>
+        <v>-19.14276140000001</v>
       </c>
       <c r="Q96">
-        <v>-36.31231128</v>
+        <v>-36.64276140000001</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.3180235323417449</v>
+        <v>0.372468238810094</v>
       </c>
       <c r="T96">
-        <v>6.286917606044915</v>
+        <v>7.544301127253902</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.1183105779500127</v>
+        <v>0.1170652034452757</v>
       </c>
       <c r="W96">
-        <v>0.207902365719387</v>
+        <v>0.208196025027604</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9323,7 +9323,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.3943685931667091</v>
+        <v>0.3902173448175857</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9331,22 +9331,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2164096357167285</v>
+        <v>0.2183096357167285</v>
       </c>
       <c r="C97">
-        <v>-131.9582776659146</v>
+        <v>-134.4385978647318</v>
       </c>
       <c r="D97">
-        <v>55.69172233408538</v>
+        <v>55.2134021352682</v>
       </c>
       <c r="E97">
-        <v>119.79</v>
+        <v>121.792</v>
       </c>
       <c r="F97">
-        <v>190.19</v>
+        <v>192.192</v>
       </c>
       <c r="G97">
         <v>2.54</v>
@@ -9367,37 +9367,37 @@
         <v>17.5</v>
       </c>
       <c r="M97">
-        <v>44.84680200000001</v>
+        <v>45.31887360000001</v>
       </c>
       <c r="N97">
-        <v>-27.34680200000001</v>
+        <v>-27.81887360000001</v>
       </c>
       <c r="O97">
-        <v>-8.204040600000003</v>
+        <v>-8.345662080000002</v>
       </c>
       <c r="P97">
-        <v>-19.14276140000001</v>
+        <v>-19.47321152000001</v>
       </c>
       <c r="Q97">
-        <v>-36.64276140000001</v>
+        <v>-36.97321152000001</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.372468238810094</v>
+        <v>0.4541352985126176</v>
       </c>
       <c r="T97">
-        <v>7.544301127253902</v>
+        <v>9.43037640906738</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.1170652034452757</v>
+        <v>0.1158457742427208</v>
       </c>
       <c r="W97">
-        <v>0.208196025027604</v>
+        <v>0.2084835664335664</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9405,7 +9405,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.3902173448175857</v>
+        <v>0.3861525808090692</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9413,22 +9413,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2183096357167285</v>
+        <v>0.2202096357167284</v>
       </c>
       <c r="C98">
-        <v>-134.4385978647318</v>
+        <v>-136.9107717206844</v>
       </c>
       <c r="D98">
-        <v>55.2134021352682</v>
+        <v>54.74322827931564</v>
       </c>
       <c r="E98">
-        <v>121.792</v>
+        <v>123.794</v>
       </c>
       <c r="F98">
-        <v>192.192</v>
+        <v>194.194</v>
       </c>
       <c r="G98">
         <v>2.54</v>
@@ -9449,37 +9449,37 @@
         <v>17.5</v>
       </c>
       <c r="M98">
-        <v>45.3188736</v>
+        <v>45.7909452</v>
       </c>
       <c r="N98">
-        <v>-27.8188736</v>
+        <v>-28.2909452</v>
       </c>
       <c r="O98">
-        <v>-8.34566208</v>
+        <v>-8.48728356</v>
       </c>
       <c r="P98">
-        <v>-19.47321152</v>
+        <v>-19.80366164</v>
       </c>
       <c r="Q98">
-        <v>-36.97321152000001</v>
+        <v>-37.30366164</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.4541352985126166</v>
+        <v>0.5902470646834886</v>
       </c>
       <c r="T98">
-        <v>9.430376409067357</v>
+        <v>12.57383521208981</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.1158457742427208</v>
+        <v>0.1146514879103216</v>
       </c>
       <c r="W98">
-        <v>0.2084835664335664</v>
+        <v>0.2087651791507462</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9487,7 +9487,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.3861525808090693</v>
+        <v>0.3821716263677387</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9495,22 +9495,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2202096357167284</v>
+        <v>0.2221096357167285</v>
       </c>
       <c r="C99">
-        <v>-136.9107717206844</v>
+        <v>-139.3750055889158</v>
       </c>
       <c r="D99">
-        <v>54.74322827931564</v>
+        <v>54.28099441108427</v>
       </c>
       <c r="E99">
-        <v>123.794</v>
+        <v>125.796</v>
       </c>
       <c r="F99">
-        <v>194.194</v>
+        <v>196.196</v>
       </c>
       <c r="G99">
         <v>2.54</v>
@@ -9531,37 +9531,37 @@
         <v>17.5</v>
       </c>
       <c r="M99">
-        <v>45.7909452</v>
+        <v>46.26301680000001</v>
       </c>
       <c r="N99">
-        <v>-28.2909452</v>
+        <v>-28.76301680000001</v>
       </c>
       <c r="O99">
-        <v>-8.48728356</v>
+        <v>-8.628905040000003</v>
       </c>
       <c r="P99">
-        <v>-19.80366164</v>
+        <v>-20.13411176000001</v>
       </c>
       <c r="Q99">
-        <v>-37.30366164</v>
+        <v>-37.63411176000001</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>0.5902470646834886</v>
+        <v>0.8624705970252331</v>
       </c>
       <c r="T99">
-        <v>12.57383521208981</v>
+        <v>18.86075281813471</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.1146514879103216</v>
+        <v>0.1134815747683795</v>
       </c>
       <c r="W99">
-        <v>0.2087651791507462</v>
+        <v>0.2090410446696161</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9569,7 +9569,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.3821716263677387</v>
+        <v>0.3782719158945985</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9577,22 +9577,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2221096357167285</v>
+        <v>0.2240096357167284</v>
       </c>
       <c r="C100">
-        <v>-139.3750055889158</v>
+        <v>-141.8314989133448</v>
       </c>
       <c r="D100">
-        <v>54.28099441108427</v>
+        <v>53.82650108665522</v>
       </c>
       <c r="E100">
-        <v>125.796</v>
+        <v>127.798</v>
       </c>
       <c r="F100">
-        <v>196.196</v>
+        <v>198.198</v>
       </c>
       <c r="G100">
         <v>2.54</v>
@@ -9613,37 +9613,37 @@
         <v>17.5</v>
       </c>
       <c r="M100">
-        <v>46.26301680000001</v>
+        <v>46.7350884</v>
       </c>
       <c r="N100">
-        <v>-28.76301680000001</v>
+        <v>-29.2350884</v>
       </c>
       <c r="O100">
-        <v>-8.628905040000003</v>
+        <v>-8.770526520000001</v>
       </c>
       <c r="P100">
-        <v>-20.13411176000001</v>
+        <v>-20.46456188</v>
       </c>
       <c r="Q100">
-        <v>-37.63411176000001</v>
+        <v>-37.96456188000001</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>0.8624705970252331</v>
+        <v>1.679141194050466</v>
       </c>
       <c r="T100">
-        <v>18.86075281813471</v>
+        <v>37.72150563626943</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.1134815747683795</v>
+        <v>0.1123352962353656</v>
       </c>
       <c r="W100">
-        <v>0.2090410446696161</v>
+        <v>0.2093113371477008</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9651,91 +9651,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.3782719158945985</v>
+        <v>0.3744509874512187</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2240096357167284</v>
-      </c>
-      <c r="C101">
-        <v>-141.8314989133448</v>
-      </c>
-      <c r="D101">
-        <v>53.82650108665522</v>
-      </c>
-      <c r="E101">
-        <v>127.798</v>
-      </c>
-      <c r="F101">
-        <v>198.198</v>
-      </c>
-      <c r="G101">
-        <v>2.54</v>
-      </c>
-      <c r="H101">
-        <v>129.8</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>0</v>
-      </c>
-      <c r="K101">
-        <v>-17.5</v>
-      </c>
-      <c r="L101">
-        <v>17.5</v>
-      </c>
-      <c r="M101">
-        <v>46.7350884</v>
-      </c>
-      <c r="N101">
-        <v>-29.2350884</v>
-      </c>
-      <c r="O101">
-        <v>-8.770526520000001</v>
-      </c>
-      <c r="P101">
-        <v>-20.46456188</v>
-      </c>
-      <c r="Q101">
-        <v>-37.96456188000001</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>1.679141194050466</v>
-      </c>
-      <c r="T101">
-        <v>37.72150563626943</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.1123352962353656</v>
-      </c>
-      <c r="W101">
-        <v>0.2093113371477008</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.3744509874512187</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
